--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.54</v>
+        <v>2.73</v>
       </c>
       <c r="O28" t="n">
-        <v>4.39</v>
+        <v>2.98</v>
       </c>
       <c r="P28" t="n">
-        <v>5.42</v>
+        <v>2.76</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.73</v>
+        <v>1.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.98</v>
+        <v>4.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.76</v>
+        <v>3.46</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>4.39</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>5.42</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>2.85</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="O21" t="n">
-        <v>3.95</v>
+        <v>4.39</v>
       </c>
       <c r="P21" t="n">
-        <v>3.9</v>
+        <v>5.42</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="O22" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O24" t="n">
-        <v>3.9</v>
+        <v>4.27</v>
       </c>
       <c r="P24" t="n">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.73</v>
+        <v>4.45</v>
       </c>
       <c r="O27" t="n">
-        <v>2.98</v>
+        <v>4.15</v>
       </c>
       <c r="P27" t="n">
-        <v>2.76</v>
+        <v>1.56</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G61" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P15" t="n">
-        <v>3.03</v>
+        <v>3.47</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.16</v>
+        <v>1.69</v>
       </c>
       <c r="O17" t="n">
-        <v>6.85</v>
+        <v>3.95</v>
       </c>
       <c r="P17" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.54</v>
+        <v>4.6</v>
       </c>
       <c r="O21" t="n">
-        <v>4.39</v>
+        <v>4.2</v>
       </c>
       <c r="P21" t="n">
-        <v>5.42</v>
+        <v>1.53</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="O22" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P22" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.69</v>
+        <v>2.85</v>
       </c>
       <c r="O23" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.8</v>
+        <v>1.16</v>
       </c>
       <c r="O24" t="n">
-        <v>4.27</v>
+        <v>6.85</v>
       </c>
       <c r="P24" t="n">
-        <v>3.46</v>
+        <v>9.6</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>4.45</v>
+        <v>1.8</v>
       </c>
       <c r="O27" t="n">
-        <v>4.15</v>
+        <v>4.27</v>
       </c>
       <c r="P27" t="n">
-        <v>1.56</v>
+        <v>3.46</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4745,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G59" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>3.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="O15" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.6</v>
+        <v>2.73</v>
       </c>
       <c r="O21" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="P21" t="n">
-        <v>1.53</v>
+        <v>2.76</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.45</v>
+        <v>1.54</v>
       </c>
       <c r="O22" t="n">
-        <v>4.15</v>
+        <v>4.39</v>
       </c>
       <c r="P22" t="n">
-        <v>1.56</v>
+        <v>5.42</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>6.85</v>
+        <v>3.69</v>
       </c>
       <c r="P24" t="n">
-        <v>9.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>4.45</v>
       </c>
       <c r="O25" t="n">
-        <v>3.69</v>
+        <v>4.15</v>
       </c>
       <c r="P25" t="n">
-        <v>3.3</v>
+        <v>1.56</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="P13" t="n">
-        <v>3.47</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="O14" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>3.03</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P15" t="n">
-        <v>3.03</v>
+        <v>3.47</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.69</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.54</v>
+        <v>4.45</v>
       </c>
       <c r="O22" t="n">
-        <v>4.39</v>
+        <v>4.15</v>
       </c>
       <c r="P22" t="n">
-        <v>5.42</v>
+        <v>1.56</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>1.69</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="P23" t="n">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="O27" t="n">
-        <v>4.27</v>
+        <v>4.39</v>
       </c>
       <c r="P27" t="n">
-        <v>3.46</v>
+        <v>5.42</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4745,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4862,10 +4862,10 @@
         <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>3.9</v>
+        <v>3.69</v>
       </c>
       <c r="P28" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O37" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P37" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O38" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P38" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N63" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>3.03</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="O15" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>1.54</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="P17" t="n">
-        <v>1.53</v>
+        <v>5.42</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>3.95</v>
+        <v>3.69</v>
       </c>
       <c r="P23" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.54</v>
+        <v>2.85</v>
       </c>
       <c r="O27" t="n">
-        <v>4.39</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>5.42</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
-        <v>3.69</v>
+        <v>4.2</v>
       </c>
       <c r="P28" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O37" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P38" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,10 +8390,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,10 +8708,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N61" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU63"/>
+  <dimension ref="A1:AU65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="O13" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.11</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.22</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="P15" t="n">
-        <v>3.03</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="O16" t="n">
-        <v>6.85</v>
+        <v>4.39</v>
       </c>
       <c r="P16" t="n">
-        <v>9.6</v>
+        <v>5.42</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>4.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.73</v>
+        <v>4.45</v>
       </c>
       <c r="O21" t="n">
-        <v>2.98</v>
+        <v>4.15</v>
       </c>
       <c r="P21" t="n">
-        <v>2.76</v>
+        <v>1.56</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.69</v>
+        <v>4.2</v>
       </c>
       <c r="P23" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="P28" t="n">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="O29" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,14 +7085,14 @@
         </is>
       </c>
       <c r="N42" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P42" t="n">
         <v>2.29</v>
       </c>
-      <c r="O42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P42" t="n">
-        <v>3.42</v>
-      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.23</v>
+        <v>2.29</v>
       </c>
       <c r="O43" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="P43" t="n">
-        <v>2.29</v>
+        <v>3.42</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,69 +8353,69 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P50" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG50" t="n">
         <v>2.3</v>
       </c>
-      <c r="O50" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P50" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
       <c r="AH50" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,10 +8708,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -8778,7 +8778,7 @@
         <v>0</v>
       </c>
       <c r="AU52" s="3" t="n">
-        <v>46187.6875</v>
+        <v>46187.66666666666</v>
       </c>
     </row>
     <row r="53">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9026,10 +9026,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.09</v>
+        <v>2.26</v>
       </c>
       <c r="O55" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="P55" t="n">
-        <v>3.93</v>
+        <v>3.36</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="AU55" s="3" t="n">
-        <v>46187.70833333334</v>
+        <v>46187.6875</v>
       </c>
     </row>
     <row r="56">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9344,10 +9344,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="AU57" s="3" t="n">
-        <v>46187.77083333334</v>
+        <v>46187.70833333334</v>
       </c>
     </row>
     <row r="58">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9732,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>46187.79166666666</v>
+        <v>46187.77083333334</v>
       </c>
     </row>
     <row r="59">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>46187.8125</v>
+        <v>46187.79166666666</v>
       </c>
     </row>
     <row r="63">
@@ -10377,156 +10377,474 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" s="3" t="n">
+        <v>46187.79166666666</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" s="3" t="n">
+        <v>46187.8125</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Blooming</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>The Strongest</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="inlineStr">
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU63" s="3" t="n">
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" s="3" t="n">
         <v>46187.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="O15" t="n">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>3.47</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.54</v>
+        <v>2.73</v>
       </c>
       <c r="O16" t="n">
-        <v>4.39</v>
+        <v>2.98</v>
       </c>
       <c r="P16" t="n">
-        <v>5.42</v>
+        <v>2.76</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>4.27</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>3.46</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.73</v>
+        <v>1.69</v>
       </c>
       <c r="O20" t="n">
-        <v>2.98</v>
+        <v>3.95</v>
       </c>
       <c r="P20" t="n">
-        <v>2.76</v>
+        <v>3.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>1.54</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="P23" t="n">
-        <v>1.53</v>
+        <v>5.42</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O24" t="n">
-        <v>3.9</v>
+        <v>4.27</v>
       </c>
       <c r="P24" t="n">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,14 +6767,14 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.58</v>
+        <v>2.29</v>
       </c>
       <c r="O40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P40" t="n">
         <v>3.42</v>
       </c>
-      <c r="P40" t="n">
-        <v>5.74</v>
-      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.53</v>
+        <v>3.23</v>
       </c>
       <c r="O41" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="P41" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.23</v>
+        <v>1.58</v>
       </c>
       <c r="O42" t="n">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="P42" t="n">
-        <v>2.29</v>
+        <v>5.74</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.29</v>
+        <v>3.53</v>
       </c>
       <c r="O43" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="P43" t="n">
-        <v>3.42</v>
+        <v>2.26</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,68 +8353,68 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,68 +8512,68 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N62" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.22</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="O15" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>1.54</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>4.39</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>5.42</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.45</v>
+        <v>1.16</v>
       </c>
       <c r="O21" t="n">
-        <v>4.15</v>
+        <v>6.85</v>
       </c>
       <c r="P21" t="n">
-        <v>1.56</v>
+        <v>9.6</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.16</v>
+        <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>6.85</v>
+        <v>3.95</v>
       </c>
       <c r="P22" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="O23" t="n">
-        <v>4.39</v>
+        <v>4.27</v>
       </c>
       <c r="P23" t="n">
-        <v>5.42</v>
+        <v>3.46</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>4.27</v>
+        <v>3.69</v>
       </c>
       <c r="P24" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>2.73</v>
       </c>
       <c r="O29" t="n">
-        <v>3.69</v>
+        <v>2.98</v>
       </c>
       <c r="P29" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,14 +6767,14 @@
         </is>
       </c>
       <c r="N40" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P40" t="n">
         <v>2.29</v>
       </c>
-      <c r="O40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P40" t="n">
-        <v>3.42</v>
-      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.23</v>
+        <v>3.53</v>
       </c>
       <c r="O41" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="P41" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.53</v>
+        <v>2.29</v>
       </c>
       <c r="O43" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="P43" t="n">
-        <v>2.26</v>
+        <v>3.42</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,69 +7876,69 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P47" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG47" t="n">
         <v>2.3</v>
       </c>
-      <c r="O47" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P47" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
       <c r="AH47" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,68 +8512,68 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G63" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="O13" t="n">
-        <v>3.67</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.11</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.22</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="P15" t="n">
-        <v>3.03</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>4.39</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>5.42</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,14 +3587,14 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="O20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P20" t="n">
         <v>3.9</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.9</v>
-      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.69</v>
+        <v>1.16</v>
       </c>
       <c r="O22" t="n">
-        <v>3.95</v>
+        <v>6.85</v>
       </c>
       <c r="P22" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="O23" t="n">
-        <v>4.27</v>
+        <v>4.39</v>
       </c>
       <c r="P23" t="n">
-        <v>3.46</v>
+        <v>5.42</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>4.45</v>
       </c>
       <c r="O24" t="n">
-        <v>3.69</v>
+        <v>4.15</v>
       </c>
       <c r="P24" t="n">
-        <v>3.3</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="O26" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="P26" t="n">
-        <v>1.53</v>
+        <v>3.46</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="O27" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O37" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P37" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O38" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P38" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.23</v>
+        <v>1.58</v>
       </c>
       <c r="O40" t="n">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="P40" t="n">
-        <v>2.29</v>
+        <v>5.74</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.58</v>
+        <v>3.23</v>
       </c>
       <c r="O42" t="n">
-        <v>3.42</v>
+        <v>2.83</v>
       </c>
       <c r="P42" t="n">
-        <v>5.74</v>
+        <v>2.29</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="P44" t="n">
-        <v>4.2</v>
+        <v>3.44</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,68 +7876,68 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9344,10 +9344,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G62" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.73</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.76</v>
+        <v>1.53</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>4.45</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>1.56</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.69</v>
+        <v>1.16</v>
       </c>
       <c r="O20" t="n">
-        <v>3.95</v>
+        <v>6.85</v>
       </c>
       <c r="P20" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.16</v>
+        <v>2.85</v>
       </c>
       <c r="O22" t="n">
-        <v>6.85</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>9.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="O23" t="n">
-        <v>4.39</v>
+        <v>4.27</v>
       </c>
       <c r="P23" t="n">
-        <v>5.42</v>
+        <v>3.46</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.45</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>4.15</v>
+        <v>3.69</v>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>3.3</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="O26" t="n">
-        <v>4.27</v>
+        <v>4.39</v>
       </c>
       <c r="P26" t="n">
-        <v>3.46</v>
+        <v>5.42</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>2.73</v>
       </c>
       <c r="O28" t="n">
-        <v>3.69</v>
+        <v>2.98</v>
       </c>
       <c r="P28" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O37" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P38" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.58</v>
+        <v>3.53</v>
       </c>
       <c r="O40" t="n">
-        <v>3.42</v>
+        <v>2.68</v>
       </c>
       <c r="P40" t="n">
-        <v>5.74</v>
+        <v>2.26</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.53</v>
+        <v>1.58</v>
       </c>
       <c r="O41" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="P41" t="n">
-        <v>2.26</v>
+        <v>5.74</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.23</v>
+        <v>2.29</v>
       </c>
       <c r="O42" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="P42" t="n">
-        <v>2.29</v>
+        <v>3.42</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,14 +7244,14 @@
         </is>
       </c>
       <c r="N43" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P43" t="n">
         <v>2.29</v>
       </c>
-      <c r="O43" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P43" t="n">
-        <v>3.42</v>
-      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8549,10 +8549,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="O53" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="P53" t="n">
-        <v>3.36</v>
+        <v>3.81</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="O54" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="P54" t="n">
-        <v>3.81</v>
+        <v>3.36</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9026,10 +9026,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G63" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>3.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>1.69</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="P17" t="n">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.45</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="O23" t="n">
-        <v>4.27</v>
+        <v>4.39</v>
       </c>
       <c r="P23" t="n">
-        <v>3.46</v>
+        <v>5.42</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>4.45</v>
       </c>
       <c r="O24" t="n">
-        <v>3.69</v>
+        <v>4.15</v>
       </c>
       <c r="P24" t="n">
-        <v>3.3</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.69</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P25" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="O26" t="n">
-        <v>4.39</v>
+        <v>4.27</v>
       </c>
       <c r="P26" t="n">
-        <v>5.42</v>
+        <v>3.46</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O37" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P37" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O38" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P38" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.53</v>
+        <v>3.23</v>
       </c>
       <c r="O40" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="P40" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.58</v>
+        <v>3.53</v>
       </c>
       <c r="O41" t="n">
-        <v>3.42</v>
+        <v>2.68</v>
       </c>
       <c r="P41" t="n">
-        <v>5.74</v>
+        <v>2.26</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.23</v>
+        <v>1.58</v>
       </c>
       <c r="O43" t="n">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="P43" t="n">
-        <v>2.29</v>
+        <v>5.74</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7558,68 +7558,68 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,10 +8390,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,69 +8512,69 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P51" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG51" t="n">
         <v>2.3</v>
       </c>
-      <c r="O51" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P51" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
       <c r="AH51" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="O53" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="P53" t="n">
-        <v>3.81</v>
+        <v>3.36</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9026,10 +9026,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N63" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.22</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="P14" t="n">
-        <v>3.03</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="O15" t="n">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>3.47</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>4.45</v>
       </c>
       <c r="O16" t="n">
-        <v>3.69</v>
+        <v>4.15</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>1.56</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.69</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.54</v>
+        <v>1.16</v>
       </c>
       <c r="O23" t="n">
-        <v>4.39</v>
+        <v>6.85</v>
       </c>
       <c r="P23" t="n">
-        <v>5.42</v>
+        <v>9.6</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.45</v>
+        <v>1.54</v>
       </c>
       <c r="O24" t="n">
-        <v>4.15</v>
+        <v>4.39</v>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>5.42</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="P25" t="n">
-        <v>1.53</v>
+        <v>3.46</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>4.27</v>
+        <v>3.69</v>
       </c>
       <c r="P26" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.16</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>6.85</v>
+        <v>3.9</v>
       </c>
       <c r="P29" t="n">
-        <v>9.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O37" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P38" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.23</v>
+        <v>2.29</v>
       </c>
       <c r="O40" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="P40" t="n">
-        <v>2.29</v>
+        <v>3.42</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.53</v>
+        <v>1.58</v>
       </c>
       <c r="O41" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="P41" t="n">
-        <v>2.26</v>
+        <v>5.74</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.29</v>
+        <v>3.53</v>
       </c>
       <c r="O42" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="P42" t="n">
-        <v>3.42</v>
+        <v>2.26</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.58</v>
+        <v>3.23</v>
       </c>
       <c r="O43" t="n">
-        <v>3.42</v>
+        <v>2.83</v>
       </c>
       <c r="P43" t="n">
-        <v>5.74</v>
+        <v>2.29</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,69 +7876,69 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P47" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG47" t="n">
         <v>2.3</v>
       </c>
-      <c r="O47" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P47" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
       <c r="AH47" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,10 +8390,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,10 +8708,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9026,10 +9026,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G62" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>1.54</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>4.39</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>5.42</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="O24" t="n">
-        <v>4.39</v>
+        <v>4.27</v>
       </c>
       <c r="P24" t="n">
-        <v>5.42</v>
+        <v>3.46</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>2.73</v>
       </c>
       <c r="O26" t="n">
-        <v>3.69</v>
+        <v>2.98</v>
       </c>
       <c r="P26" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>4.6</v>
+        <v>1.16</v>
       </c>
       <c r="O30" t="n">
-        <v>4.2</v>
+        <v>6.85</v>
       </c>
       <c r="P30" t="n">
-        <v>1.53</v>
+        <v>9.6</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,14 +6767,14 @@
         </is>
       </c>
       <c r="N40" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P40" t="n">
         <v>2.29</v>
       </c>
-      <c r="O40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P40" t="n">
-        <v>3.42</v>
-      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,14 +6926,14 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.58</v>
+        <v>2.29</v>
       </c>
       <c r="O41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P41" t="n">
         <v>3.42</v>
       </c>
-      <c r="P41" t="n">
-        <v>5.74</v>
-      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.23</v>
+        <v>1.58</v>
       </c>
       <c r="O43" t="n">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="P43" t="n">
-        <v>2.29</v>
+        <v>5.74</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,68 +7876,68 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="O47" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="Z47" t="n">
-        <v>7.5</v>
+        <v>2.45</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="P48" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.47</v>
+        <v>1.06</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.45</v>
+        <v>7.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,10 +8708,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N63" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.54</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>4.39</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>5.42</v>
+        <v>1.53</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>4.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.69</v>
+        <v>2.73</v>
       </c>
       <c r="O21" t="n">
-        <v>3.95</v>
+        <v>2.98</v>
       </c>
       <c r="P21" t="n">
-        <v>3.9</v>
+        <v>2.76</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>4.27</v>
+        <v>3.9</v>
       </c>
       <c r="P24" t="n">
-        <v>3.46</v>
+        <v>2.9</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="O26" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O37" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P37" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O38" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P38" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.29</v>
+        <v>3.53</v>
       </c>
       <c r="O41" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="P41" t="n">
-        <v>3.42</v>
+        <v>2.26</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.53</v>
+        <v>1.58</v>
       </c>
       <c r="O42" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="P42" t="n">
-        <v>2.26</v>
+        <v>5.74</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,14 +7244,14 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.58</v>
+        <v>2.29</v>
       </c>
       <c r="O43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P43" t="n">
         <v>3.42</v>
       </c>
-      <c r="P43" t="n">
-        <v>5.74</v>
-      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="P47" t="n">
-        <v>4.2</v>
+        <v>3.44</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,64 +8675,64 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10420,17 +10420,17 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.67</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.99</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>3.47</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>46187.41666666666</v>
+        <v>46187.45833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.69</v>
+        <v>1.16</v>
       </c>
       <c r="O16" t="n">
-        <v>3.95</v>
+        <v>6.85</v>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>9.6</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="P17" t="n">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.45</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4.15</v>
+        <v>3.67</v>
       </c>
       <c r="P18" t="n">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.8</v>
+        <v>4.45</v>
       </c>
       <c r="O19" t="n">
-        <v>4.27</v>
+        <v>4.15</v>
       </c>
       <c r="P19" t="n">
-        <v>3.46</v>
+        <v>1.56</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3473,10 +3473,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.16</v>
+        <v>1.8</v>
       </c>
       <c r="O20" t="n">
-        <v>6.85</v>
+        <v>4.27</v>
       </c>
       <c r="P20" t="n">
-        <v>9.6</v>
+        <v>3.46</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.73</v>
+        <v>1.69</v>
       </c>
       <c r="O21" t="n">
-        <v>2.98</v>
+        <v>3.95</v>
       </c>
       <c r="P21" t="n">
-        <v>2.76</v>
+        <v>3.9</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4268,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4745,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>46187.45833333334</v>
+        <v>46187.5</v>
       </c>
     </row>
     <row r="31">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O37" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O38" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P38" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6494,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,68 +7399,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,17 +7876,17 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,10 +8390,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,68 +8671,68 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="O52" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="Z52" t="n">
-        <v>7.5</v>
+        <v>2.45</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9026,10 +9026,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9344,10 +9344,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="O17" t="n">
-        <v>3.69</v>
+        <v>4.39</v>
       </c>
       <c r="P17" t="n">
-        <v>3.3</v>
+        <v>5.42</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.45</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>4.15</v>
+        <v>3.69</v>
       </c>
       <c r="P19" t="n">
-        <v>1.56</v>
+        <v>3.3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3.95</v>
+        <v>4.27</v>
       </c>
       <c r="P21" t="n">
-        <v>3.9</v>
+        <v>3.46</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="O23" t="n">
-        <v>4.39</v>
+        <v>3.95</v>
       </c>
       <c r="P23" t="n">
-        <v>5.42</v>
+        <v>3.9</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4745,10 +4745,10 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3.23</v>
+        <v>1.58</v>
       </c>
       <c r="O40" t="n">
-        <v>2.83</v>
+        <v>3.42</v>
       </c>
       <c r="P40" t="n">
-        <v>2.29</v>
+        <v>5.74</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6800,10 +6800,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.58</v>
+        <v>3.23</v>
       </c>
       <c r="O42" t="n">
-        <v>3.42</v>
+        <v>2.83</v>
       </c>
       <c r="P42" t="n">
-        <v>5.74</v>
+        <v>2.29</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7399,68 +7399,68 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,10 +8390,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="O53" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="P53" t="n">
-        <v>3.36</v>
+        <v>3.81</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="O55" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="P55" t="n">
-        <v>3.81</v>
+        <v>3.36</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10102,17 +10102,17 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N65" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU65"/>
+  <dimension ref="A1:AU69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="O17" t="n">
-        <v>4.39</v>
+        <v>3.95</v>
       </c>
       <c r="P17" t="n">
-        <v>5.42</v>
+        <v>3.9</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3.69</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
-        <v>4.27</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>3.46</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.45</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>1.56</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P24" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4904,10 +4904,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.43</v>
+        <v>1.88</v>
       </c>
       <c r="O33" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P33" t="n">
-        <v>2.6</v>
+        <v>3.98</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5766,27 +5766,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>46187.54166666666</v>
+        <v>46187.5</v>
       </c>
     </row>
     <row r="35">
@@ -5925,27 +5925,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="AU35" s="3" t="n">
-        <v>46187.55208333334</v>
+        <v>46187.5</v>
       </c>
     </row>
     <row r="36">
@@ -6084,27 +6084,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <v>46187.5625</v>
+        <v>46187.5</v>
       </c>
     </row>
     <row r="37">
@@ -6243,27 +6243,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6335,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="AU37" s="3" t="n">
-        <v>46187.58333333334</v>
+        <v>46187.5</v>
       </c>
     </row>
     <row r="38">
@@ -6402,12 +6402,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="AU38" s="3" t="n">
-        <v>46187.58333333334</v>
+        <v>46187.54166666666</v>
       </c>
     </row>
     <row r="39">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6641,10 +6641,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6711,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="AU39" s="3" t="n">
-        <v>46187.625</v>
+        <v>46187.55208333334</v>
       </c>
     </row>
     <row r="40">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>46187.64583333334</v>
+        <v>46187.5625</v>
       </c>
     </row>
     <row r="41">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.53</v>
+        <v>1.68</v>
       </c>
       <c r="O41" t="n">
-        <v>2.68</v>
+        <v>4.3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.26</v>
+        <v>4.08</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="3" t="n">
-        <v>46187.64583333334</v>
+        <v>46187.58333333334</v>
       </c>
     </row>
     <row r="42">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
-        <v>2.83</v>
+        <v>3.82</v>
       </c>
       <c r="P42" t="n">
-        <v>2.29</v>
+        <v>2.07</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="AU42" s="3" t="n">
-        <v>46187.64583333334</v>
+        <v>46187.58333333334</v>
       </c>
     </row>
     <row r="43">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.29</v>
+        <v>1.82</v>
       </c>
       <c r="O43" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="P43" t="n">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7347,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="AU43" s="3" t="n">
-        <v>46187.64583333334</v>
+        <v>46187.625</v>
       </c>
     </row>
     <row r="44">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>5.74</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="AU44" s="3" t="n">
-        <v>46187.66666666666</v>
+        <v>46187.64583333334</v>
       </c>
     </row>
     <row r="45">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46187.66666666666</v>
+        <v>46187.64583333334</v>
       </c>
     </row>
     <row r="46">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="AU46" s="3" t="n">
-        <v>46187.66666666666</v>
+        <v>46187.64583333334</v>
       </c>
     </row>
     <row r="47">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
-        <v>46187.66666666666</v>
+        <v>46187.64583333334</v>
       </c>
     </row>
     <row r="48">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="O48" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="Z48" t="n">
-        <v>7.5</v>
+        <v>2.45</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="O49" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>3.44</v>
+        <v>3.02</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="P52" t="n">
-        <v>4.2</v>
+        <v>3.44</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,10 +8708,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -8787,12 +8787,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.12</v>
+        <v>1.36</v>
       </c>
       <c r="O53" t="n">
-        <v>2.74</v>
+        <v>4.8</v>
       </c>
       <c r="P53" t="n">
-        <v>3.81</v>
+        <v>5.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.15</v>
+        <v>7.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8937,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="AU53" s="3" t="n">
-        <v>46187.6875</v>
+        <v>46187.66666666666</v>
       </c>
     </row>
     <row r="54">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -9096,7 +9096,7 @@
         <v>0</v>
       </c>
       <c r="AU54" s="3" t="n">
-        <v>46187.6875</v>
+        <v>46187.66666666666</v>
       </c>
     </row>
     <row r="55">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="AU55" s="3" t="n">
-        <v>46187.6875</v>
+        <v>46187.66666666666</v>
       </c>
     </row>
     <row r="56">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9344,10 +9344,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -9414,7 +9414,7 @@
         <v>0</v>
       </c>
       <c r="AU56" s="3" t="n">
-        <v>46187.70833333334</v>
+        <v>46187.66666666666</v>
       </c>
     </row>
     <row r="57">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="AU57" s="3" t="n">
-        <v>46187.70833333334</v>
+        <v>46187.6875</v>
       </c>
     </row>
     <row r="58">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9732,7 +9732,7 @@
         <v>0</v>
       </c>
       <c r="AU58" s="3" t="n">
-        <v>46187.77083333334</v>
+        <v>46187.6875</v>
       </c>
     </row>
     <row r="59">
@@ -9741,12 +9741,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,10 +9821,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="AU59" s="3" t="n">
-        <v>46187.79166666666</v>
+        <v>46187.6875</v>
       </c>
     </row>
     <row r="60">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46187.79166666666</v>
+        <v>46187.70833333334</v>
       </c>
     </row>
     <row r="61">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="O61" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="P61" t="n">
-        <v>4.16</v>
+        <v>3.93</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46187.79166666666</v>
+        <v>46187.70833333334</v>
       </c>
     </row>
     <row r="62">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>46187.79166666666</v>
+        <v>46187.77083333334</v>
       </c>
     </row>
     <row r="63">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10616,10 +10616,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -10686,7 +10686,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="3" t="n">
-        <v>46187.8125</v>
+        <v>46187.79166666666</v>
       </c>
     </row>
     <row r="65">
@@ -10695,156 +10695,792 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" s="3" t="n">
+        <v>46187.79166666666</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Real Potosí</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" s="3" t="n">
+        <v>46187.79166666666</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" s="3" t="n">
+        <v>46187.79166666666</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" s="3" t="n">
+        <v>46187.8125</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Blooming</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>The Strongest</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="inlineStr">
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU65" s="3" t="n">
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" s="3" t="n">
         <v>46187.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>3.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.67</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.11</v>
+        <v>1.53</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.69</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.95</v>
+        <v>3.67</v>
       </c>
       <c r="P17" t="n">
-        <v>3.9</v>
+        <v>2.11</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>1.54</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.53</v>
+        <v>5.42</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.16</v>
+        <v>2.85</v>
       </c>
       <c r="O20" t="n">
-        <v>6.85</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>9.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>4.45</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3950,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.45</v>
+        <v>1.8</v>
       </c>
       <c r="O24" t="n">
-        <v>4.15</v>
+        <v>4.27</v>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>3.46</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>4.39</v>
+        <v>3.69</v>
       </c>
       <c r="P27" t="n">
-        <v>5.42</v>
+        <v>3.3</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.8</v>
+        <v>1.16</v>
       </c>
       <c r="O28" t="n">
-        <v>4.27</v>
+        <v>6.85</v>
       </c>
       <c r="P28" t="n">
-        <v>3.46</v>
+        <v>9.6</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P41" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O42" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.58</v>
+        <v>3.53</v>
       </c>
       <c r="O44" t="n">
-        <v>3.42</v>
+        <v>2.68</v>
       </c>
       <c r="P44" t="n">
-        <v>5.74</v>
+        <v>2.26</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,14 +7562,14 @@
         </is>
       </c>
       <c r="N45" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P45" t="n">
         <v>2.29</v>
       </c>
-      <c r="O45" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P45" t="n">
-        <v>3.42</v>
-      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.53</v>
+        <v>1.58</v>
       </c>
       <c r="O46" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="P46" t="n">
-        <v>2.26</v>
+        <v>5.74</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3.23</v>
+        <v>2.29</v>
       </c>
       <c r="O47" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="P47" t="n">
-        <v>2.29</v>
+        <v>3.42</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,17 +8035,17 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,10 +8072,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>1.9</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="O52" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>3.44</v>
+        <v>3.02</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,10 +8708,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="O53" t="n">
-        <v>4.8</v>
+        <v>2.67</v>
       </c>
       <c r="P53" t="n">
-        <v>5.75</v>
+        <v>3.44</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.06</v>
+        <v>1.7</v>
       </c>
       <c r="Z53" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="O57" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="P57" t="n">
-        <v>3.36</v>
+        <v>3.81</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9662,10 +9662,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,10 +9821,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="O60" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="P60" t="n">
-        <v>3.3</v>
+        <v>3.93</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="O61" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="P61" t="n">
-        <v>3.93</v>
+        <v>3.3</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10579,17 +10579,17 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10616,10 +10616,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10775,10 +10775,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.95</v>
+        <v>3.69</v>
       </c>
       <c r="P15" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>1.16</v>
       </c>
       <c r="O17" t="n">
-        <v>3.67</v>
+        <v>6.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>9.6</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>4.39</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>5.42</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.85</v>
+        <v>1.54</v>
       </c>
       <c r="O20" t="n">
-        <v>3.4</v>
+        <v>4.39</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>5.42</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>4.45</v>
+        <v>1.91</v>
       </c>
       <c r="O21" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.56</v>
+        <v>3.75</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.23</v>
+        <v>4.45</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.74</v>
+        <v>1.56</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>4.27</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="O24" t="n">
-        <v>4.27</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>3.46</v>
+        <v>2.74</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>8.6</v>
+        <v>2.85</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>3.15</v>
       </c>
       <c r="O27" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="P27" t="n">
-        <v>3.3</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.16</v>
+        <v>1.69</v>
       </c>
       <c r="O28" t="n">
-        <v>6.85</v>
+        <v>3.95</v>
       </c>
       <c r="P28" t="n">
-        <v>9.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O41" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6971,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P42" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.53</v>
+        <v>1.58</v>
       </c>
       <c r="O44" t="n">
-        <v>2.68</v>
+        <v>3.42</v>
       </c>
       <c r="P44" t="n">
-        <v>2.26</v>
+        <v>5.74</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.23</v>
+        <v>3.53</v>
       </c>
       <c r="O45" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="P45" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,10 +7595,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.58</v>
+        <v>3.23</v>
       </c>
       <c r="O46" t="n">
-        <v>3.42</v>
+        <v>2.83</v>
       </c>
       <c r="P46" t="n">
-        <v>5.74</v>
+        <v>2.29</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,10 +7754,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,17 +8035,17 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.9</v>
+        <v>2.44</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="P52" t="n">
-        <v>3.02</v>
+        <v>3.44</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,10 +8708,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="O53" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,10 +8867,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="Z53" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="P58" t="n">
-        <v>3.36</v>
+        <v>2.55</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9662,10 +9662,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,10 +9821,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="O60" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="P60" t="n">
-        <v>3.93</v>
+        <v>3.3</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="O61" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="P61" t="n">
-        <v>3.3</v>
+        <v>3.93</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="O63" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="P63" t="n">
-        <v>4.53</v>
+        <v>3.57</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="O65" t="n">
-        <v>3.02</v>
+        <v>3.72</v>
       </c>
       <c r="P65" t="n">
-        <v>4.16</v>
+        <v>4.53</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10775,10 +10775,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,13 +10901,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10934,10 +10934,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>3.03</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="P15" t="n">
-        <v>3.3</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>1.54</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>4.39</v>
       </c>
       <c r="P16" t="n">
-        <v>1.53</v>
+        <v>5.42</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.16</v>
+        <v>1.91</v>
       </c>
       <c r="O17" t="n">
-        <v>6.85</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>9.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>4.45</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>1.56</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="O20" t="n">
-        <v>4.39</v>
+        <v>4.27</v>
       </c>
       <c r="P20" t="n">
-        <v>5.42</v>
+        <v>3.46</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="P21" t="n">
-        <v>3.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.45</v>
+        <v>1.16</v>
       </c>
       <c r="O22" t="n">
-        <v>4.15</v>
+        <v>6.85</v>
       </c>
       <c r="P22" t="n">
-        <v>1.56</v>
+        <v>9.6</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.23</v>
+        <v>4.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.74</v>
+        <v>1.53</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>8.6</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>3.69</v>
       </c>
       <c r="P25" t="n">
-        <v>1.29</v>
+        <v>3.3</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.15</v>
+        <v>2.87</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>3.15</v>
+        <v>8.6</v>
       </c>
       <c r="O27" t="n">
-        <v>3.67</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.11</v>
+        <v>1.29</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.43</v>
+        <v>1.88</v>
       </c>
       <c r="O30" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>3.98</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.88</v>
+        <v>2.43</v>
       </c>
       <c r="O35" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P35" t="n">
-        <v>3.98</v>
+        <v>2.6</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,14 +7403,14 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.58</v>
+        <v>2.29</v>
       </c>
       <c r="O44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P44" t="n">
         <v>3.42</v>
       </c>
-      <c r="P44" t="n">
-        <v>5.74</v>
-      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
@@ -7436,10 +7436,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.29</v>
+        <v>1.58</v>
       </c>
       <c r="O47" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="P47" t="n">
-        <v>3.42</v>
+        <v>5.74</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,10 +7913,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9307,68 +9307,68 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="O57" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="P57" t="n">
-        <v>3.81</v>
+        <v>3.36</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,10 +9503,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="O59" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="P59" t="n">
-        <v>3.36</v>
+        <v>3.81</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,10 +9821,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="O60" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="P60" t="n">
-        <v>3.3</v>
+        <v>3.93</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9980,10 +9980,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="O61" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="P61" t="n">
-        <v>3.93</v>
+        <v>3.3</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,10 +10139,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10420,17 +10420,17 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10579,17 +10579,17 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10616,10 +10616,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,55 +10901,55 @@
         </is>
       </c>
       <c r="N66" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O66" t="n">
+        <v>5</v>
+      </c>
+      <c r="P66" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
         <v>2</v>
       </c>
-      <c r="O66" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P66" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N69" t="n">

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3.67</v>
+        <v>4.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>3.46</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.54</v>
+        <v>8.6</v>
       </c>
       <c r="O16" t="n">
-        <v>4.39</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>5.42</v>
+        <v>1.29</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.91</v>
+        <v>1.16</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>6.85</v>
       </c>
       <c r="P17" t="n">
-        <v>3.75</v>
+        <v>9.6</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.15</v>
+        <v>2.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>4.45</v>
+        <v>1.91</v>
       </c>
       <c r="O19" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.56</v>
+        <v>3.75</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="O20" t="n">
-        <v>4.27</v>
+        <v>3.95</v>
       </c>
       <c r="P20" t="n">
-        <v>3.46</v>
+        <v>3.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.23</v>
+        <v>2.85</v>
       </c>
       <c r="O21" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.16</v>
+        <v>2.23</v>
       </c>
       <c r="O22" t="n">
-        <v>6.85</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
-        <v>9.6</v>
+        <v>2.74</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="O25" t="n">
-        <v>3.69</v>
+        <v>4.39</v>
       </c>
       <c r="P25" t="n">
-        <v>3.3</v>
+        <v>5.42</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>8.6</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>3.69</v>
       </c>
       <c r="P27" t="n">
-        <v>1.29</v>
+        <v>3.3</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.69</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
-        <v>3.95</v>
+        <v>3.67</v>
       </c>
       <c r="P28" t="n">
-        <v>3.9</v>
+        <v>2.11</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.25</v>
+        <v>4.45</v>
       </c>
       <c r="O29" t="n">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="P29" t="n">
-        <v>3.14</v>
+        <v>1.56</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.88</v>
+        <v>2.73</v>
       </c>
       <c r="O30" t="n">
-        <v>3.52</v>
+        <v>2.98</v>
       </c>
       <c r="P30" t="n">
-        <v>3.98</v>
+        <v>2.76</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.73</v>
+        <v>1.88</v>
       </c>
       <c r="O33" t="n">
-        <v>2.98</v>
+        <v>3.52</v>
       </c>
       <c r="P33" t="n">
-        <v>2.76</v>
+        <v>3.98</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC41" t="n">
         <v>1.81</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7283,10 +7283,10 @@
         <v>2.37</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -7442,10 +7442,10 @@
         <v>2.1</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.53</v>
+        <v>3.23</v>
       </c>
       <c r="O45" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="P45" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,16 +7595,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="Z45" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.23</v>
+        <v>3.53</v>
       </c>
       <c r="O46" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="P46" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,16 +7754,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.1</v>
+        <v>2.44</v>
       </c>
       <c r="O48" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>1.9</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,10 +8231,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="O51" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="P51" t="n">
-        <v>4.1</v>
+        <v>3.44</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8549,16 +8549,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,65 +8675,65 @@
         </is>
       </c>
       <c r="N52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P52" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W52" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG52" t="n">
         <v>2.3</v>
       </c>
-      <c r="O52" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P52" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="P53" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,16 +8867,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="O54" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P54" t="n">
-        <v>5.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="O57" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="P57" t="n">
-        <v>3.36</v>
+        <v>2.55</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,16 +9503,16 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="O58" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="P58" t="n">
-        <v>2.55</v>
+        <v>3.81</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9662,16 +9662,16 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="O59" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="P59" t="n">
-        <v>3.81</v>
+        <v>3.36</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,16 +9821,16 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="O60" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="P60" t="n">
-        <v>3.93</v>
+        <v>3.3</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9980,16 +9980,16 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="O61" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="P61" t="n">
-        <v>3.3</v>
+        <v>3.93</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,16 +10139,16 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10420,17 +10420,17 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>2.45</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10897,17 +10897,17 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10946,10 +10946,10 @@
         <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="O67" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="P67" t="n">
-        <v>3.57</v>
+        <v>6</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,16 +11099,16 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.15</v>
+        <v>1.4</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.6</v>
+        <v>2.87</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>3.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>4.27</v>
+        <v>3.67</v>
       </c>
       <c r="P15" t="n">
-        <v>3.46</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>8.6</v>
+        <v>1.91</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.29</v>
+        <v>3.75</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.16</v>
+        <v>8.6</v>
       </c>
       <c r="O17" t="n">
-        <v>6.85</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>9.6</v>
+        <v>1.29</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>4.39</v>
       </c>
       <c r="P18" t="n">
-        <v>2.9</v>
+        <v>5.42</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="P19" t="n">
-        <v>3.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P20" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>1.16</v>
       </c>
       <c r="O21" t="n">
-        <v>3.4</v>
+        <v>6.85</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.23</v>
+        <v>2.85</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.74</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="O24" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P24" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="O25" t="n">
-        <v>4.39</v>
+        <v>4.27</v>
       </c>
       <c r="P25" t="n">
-        <v>5.42</v>
+        <v>3.46</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="P28" t="n">
-        <v>2.11</v>
+        <v>3.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="O29" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P29" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="O32" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="O33" t="n">
-        <v>3.52</v>
+        <v>2.95</v>
       </c>
       <c r="P33" t="n">
-        <v>3.98</v>
+        <v>3.2</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P41" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O42" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.82</v>
+        <v>3.53</v>
       </c>
       <c r="O43" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="P43" t="n">
-        <v>4.5</v>
+        <v>2.26</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7277,16 +7277,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -7347,7 +7347,7 @@
         <v>0</v>
       </c>
       <c r="AU43" s="3" t="n">
-        <v>46187.625</v>
+        <v>46187.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="O44" t="n">
         <v>2.7</v>
       </c>
       <c r="P44" t="n">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,16 +7436,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="AU44" s="3" t="n">
-        <v>46187.64583333334</v>
+        <v>46187.625</v>
       </c>
     </row>
     <row r="45">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.23</v>
+        <v>1.82</v>
       </c>
       <c r="O45" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="P45" t="n">
-        <v>2.29</v>
+        <v>4.5</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,16 +7595,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AU45" s="3" t="n">
-        <v>46187.64583333334</v>
+        <v>46187.625</v>
       </c>
     </row>
     <row r="46">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3.53</v>
+        <v>2.29</v>
       </c>
       <c r="O46" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="P46" t="n">
-        <v>2.26</v>
+        <v>3.42</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,16 +7754,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Z46" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="O47" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="P47" t="n">
-        <v>5.74</v>
+        <v>3.35</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,16 +7913,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -7992,12 +7992,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.44</v>
+        <v>1.58</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="P48" t="n">
-        <v>3.02</v>
+        <v>5.74</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="AU48" s="3" t="n">
-        <v>46187.66666666666</v>
+        <v>46187.64583333334</v>
       </c>
     </row>
     <row r="49">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.9</v>
+        <v>2.44</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>4.2</v>
+        <v>3.02</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,16 +8231,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="O50" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="P50" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="O51" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="P51" t="n">
-        <v>3.44</v>
+        <v>4.1</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8549,16 +8549,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,64 +8675,64 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="O52" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="P52" t="n">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="AB52" t="n">
-        <v>3.2</v>
+        <v>1.44</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,49 +8834,49 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="O53" t="n">
-        <v>3.03</v>
+        <v>2.67</v>
       </c>
       <c r="P53" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z53" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
       <c r="AA53" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O54" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P54" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9026,16 +9026,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,13 +9152,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="O55" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="P55" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9307,17 +9307,17 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9466,17 +9466,17 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="AU57" s="3" t="n">
-        <v>46187.6875</v>
+        <v>46187.66666666666</v>
       </c>
     </row>
     <row r="58">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="O60" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="P60" t="n">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46187.70833333334</v>
+        <v>46187.6875</v>
       </c>
     </row>
     <row r="61">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="O61" t="n">
-        <v>2.73</v>
+        <v>2.93</v>
       </c>
       <c r="P61" t="n">
-        <v>3.93</v>
+        <v>3.3</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10139,16 +10139,16 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="O63" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="P63" t="n">
-        <v>3.57</v>
+        <v>4.53</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O64" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="P64" t="n">
-        <v>4.16</v>
+        <v>3.57</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10616,16 +10616,16 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="O65" t="n">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="P65" t="n">
-        <v>4.53</v>
+        <v>4.16</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10775,16 +10775,16 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.47</v>
+        <v>3.03</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>3.03</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>4.45</v>
       </c>
       <c r="O15" t="n">
-        <v>3.67</v>
+        <v>4.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>1.56</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.91</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="P16" t="n">
-        <v>3.75</v>
+        <v>2.11</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>8.6</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>3.69</v>
       </c>
       <c r="P17" t="n">
-        <v>1.29</v>
+        <v>3.3</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="O18" t="n">
-        <v>4.39</v>
+        <v>4.27</v>
       </c>
       <c r="P18" t="n">
-        <v>5.42</v>
+        <v>3.46</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="O20" t="n">
-        <v>3.9</v>
+        <v>4.39</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9</v>
+        <v>5.42</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.85</v>
+        <v>1.91</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,13 +4223,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.45</v>
+        <v>1.69</v>
       </c>
       <c r="O24" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>3.9</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="O25" t="n">
-        <v>4.27</v>
+        <v>3.4</v>
       </c>
       <c r="P25" t="n">
-        <v>3.46</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.69</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P26" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>1.16</v>
       </c>
       <c r="O28" t="n">
-        <v>3.69</v>
+        <v>6.85</v>
       </c>
       <c r="P28" t="n">
-        <v>3.3</v>
+        <v>9.6</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="O29" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="P29" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.98</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>3.45</v>
+        <v>2.08</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="O34" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P36" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="O46" t="n">
         <v>2.7</v>
       </c>
       <c r="P46" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z46" t="n">
         <v>2.1</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="O47" t="n">
         <v>2.7</v>
       </c>
       <c r="P47" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z47" t="n">
         <v>2.1</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>1.85</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P49" t="n">
-        <v>3.02</v>
+        <v>4.33</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -8231,16 +8231,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="O50" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P50" t="n">
-        <v>5.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="O51" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="P51" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -8555,10 +8555,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="O52" t="n">
-        <v>3.05</v>
+        <v>2.67</v>
       </c>
       <c r="P52" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,16 +8708,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8867,16 +8867,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,13 +8993,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.85</v>
+        <v>2.44</v>
       </c>
       <c r="O54" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P54" t="n">
-        <v>4.33</v>
+        <v>3.02</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9026,16 +9026,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>3.3</v>
+        <v>1.36</v>
       </c>
       <c r="O55" t="n">
-        <v>3.03</v>
+        <v>4.8</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="O56" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="P56" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9466,17 +9466,17 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9573,7 +9573,7 @@
         <v>0</v>
       </c>
       <c r="AU57" s="3" t="n">
-        <v>46187.66666666666</v>
+        <v>46187.6875</v>
       </c>
     </row>
     <row r="58">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="O58" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="P58" t="n">
-        <v>3.81</v>
+        <v>3.36</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9662,16 +9662,16 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA58" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="O59" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="P59" t="n">
-        <v>3.36</v>
+        <v>3.81</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,16 +9821,16 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -9947,13 +9947,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="O60" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="P60" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="AU60" s="3" t="n">
-        <v>46187.6875</v>
+        <v>46187.70833333334</v>
       </c>
     </row>
     <row r="61">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -10106,13 +10106,13 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2.33</v>
+        <v>1.51</v>
       </c>
       <c r="O61" t="n">
-        <v>2.93</v>
+        <v>3.83</v>
       </c>
       <c r="P61" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.87</v>
+        <v>1.7</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="AU61" s="3" t="n">
-        <v>46187.70833333334</v>
+        <v>46187.77083333334</v>
       </c>
     </row>
     <row r="62">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="O62" t="n">
-        <v>3.83</v>
+        <v>3.72</v>
       </c>
       <c r="P62" t="n">
-        <v>5</v>
+        <v>4.53</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10368,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AU62" s="3" t="n">
-        <v>46187.77083333334</v>
+        <v>46187.79166666666</v>
       </c>
     </row>
     <row r="63">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,13 +10424,13 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="P63" t="n">
-        <v>4.53</v>
+        <v>4.16</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10457,16 +10457,16 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="O64" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>3.57</v>
+        <v>6</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,16 +10622,16 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.15</v>
+        <v>1.4</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.6</v>
+        <v>2.87</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,13 +10742,13 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O65" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="P65" t="n">
-        <v>4.16</v>
+        <v>3.57</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10775,16 +10775,16 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -11013,12 +11013,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,13 +11060,13 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="O67" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="P67" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -11099,16 +11099,16 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="AU67" s="3" t="n">
-        <v>46187.79166666666</v>
+        <v>46187.8125</v>
       </c>
     </row>
     <row r="68">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,13 +11219,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O68" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P68" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q68" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.48</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.45</v>
+        <v>1.16</v>
       </c>
       <c r="O15" t="n">
-        <v>4.15</v>
+        <v>6.85</v>
       </c>
       <c r="P15" t="n">
-        <v>1.56</v>
+        <v>9.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="P17" t="n">
-        <v>3.3</v>
+        <v>2.11</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="O18" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>3.46</v>
+        <v>1.53</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="O22" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
-        <v>3.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>8.6</v>
       </c>
       <c r="O23" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>3.14</v>
+        <v>1.29</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="P26" t="n">
-        <v>1.53</v>
+        <v>3.3</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O27" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.16</v>
+        <v>4.45</v>
       </c>
       <c r="O28" t="n">
-        <v>6.85</v>
+        <v>4.15</v>
       </c>
       <c r="P28" t="n">
-        <v>9.6</v>
+        <v>1.56</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>8.6</v>
+        <v>1.8</v>
       </c>
       <c r="O29" t="n">
-        <v>5</v>
+        <v>4.27</v>
       </c>
       <c r="P29" t="n">
-        <v>1.29</v>
+        <v>3.46</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="P32" t="n">
-        <v>2.08</v>
+        <v>3.98</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.98</v>
+        <v>2.43</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P34" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.73</v>
+        <v>1.98</v>
       </c>
       <c r="O35" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="P35" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O41" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O42" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P42" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="O44" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="P44" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7436,16 +7436,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="O45" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="P45" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7595,16 +7595,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="O46" t="n">
         <v>2.7</v>
       </c>
       <c r="P46" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z46" t="n">
         <v>2.1</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.29</v>
+        <v>1.58</v>
       </c>
       <c r="O47" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="P47" t="n">
-        <v>3.42</v>
+        <v>5.74</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7913,16 +7913,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="O48" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="P48" t="n">
-        <v>5.74</v>
+        <v>3.35</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,16 +8072,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>3.3</v>
+        <v>1.36</v>
       </c>
       <c r="O51" t="n">
-        <v>3.03</v>
+        <v>4.8</v>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="O52" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>3.44</v>
+        <v>3.02</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,16 +8708,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,17 +8989,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.36</v>
+        <v>3.3</v>
       </c>
       <c r="O55" t="n">
-        <v>4.8</v>
+        <v>3.03</v>
       </c>
       <c r="P55" t="n">
-        <v>5.75</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB55" t="n">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="O56" t="n">
-        <v>3.05</v>
+        <v>2.67</v>
       </c>
       <c r="P56" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -9344,16 +9344,16 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="O57" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="P57" t="n">
-        <v>2.55</v>
+        <v>3.81</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,16 +9503,16 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,13 +9629,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="P58" t="n">
-        <v>3.36</v>
+        <v>2.55</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -9662,16 +9662,16 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="O59" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="P59" t="n">
-        <v>3.81</v>
+        <v>3.36</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,16 +9821,16 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="O62" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="P62" t="n">
-        <v>4.53</v>
+        <v>3.57</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,55 +10424,55 @@
         </is>
       </c>
       <c r="N63" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O63" t="n">
+        <v>5</v>
+      </c>
+      <c r="P63" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC63" t="n">
         <v>2</v>
       </c>
-      <c r="O63" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P63" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>0</v>
-      </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="O64" t="n">
-        <v>5</v>
+        <v>3.02</v>
       </c>
       <c r="P64" t="n">
-        <v>6</v>
+        <v>4.16</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10616,22 +10616,22 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.87</v>
+        <v>1.47</v>
       </c>
       <c r="AC64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10738,17 +10738,17 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10897,17 +10897,17 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>5.01</v>
+        <v>4.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.16</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
-        <v>6.85</v>
+        <v>4.27</v>
       </c>
       <c r="P15" t="n">
-        <v>9.6</v>
+        <v>3.46</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.67</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>1.53</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>4.2</v>
+        <v>3.66</v>
       </c>
       <c r="P18" t="n">
-        <v>1.53</v>
+        <v>6.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.87</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.87</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.82</v>
+        <v>1.16</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="O20" t="n">
-        <v>4.39</v>
+        <v>4.28</v>
       </c>
       <c r="P20" t="n">
-        <v>5.42</v>
+        <v>5.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="O21" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="P21" t="n">
-        <v>3.14</v>
+        <v>2.74</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.23</v>
+        <v>8.6</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.74</v>
+        <v>1.29</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>8.6</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>1.29</v>
+        <v>2.9</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.69</v>
+        <v>3.15</v>
       </c>
       <c r="O24" t="n">
-        <v>3.95</v>
+        <v>3.67</v>
       </c>
       <c r="P24" t="n">
-        <v>3.9</v>
+        <v>2.11</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.44</v>
+        <v>1.84</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.7</v>
+        <v>1.86</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.85</v>
+        <v>1.16</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>6.85</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>4.45</v>
       </c>
       <c r="O26" t="n">
-        <v>3.69</v>
+        <v>4.15</v>
       </c>
       <c r="P26" t="n">
-        <v>3.3</v>
+        <v>1.56</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="P27" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>4.45</v>
+        <v>1.91</v>
       </c>
       <c r="O28" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>1.56</v>
+        <v>3.75</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>4.27</v>
+        <v>3.69</v>
       </c>
       <c r="P29" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.88</v>
+        <v>2.43</v>
       </c>
       <c r="O32" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P32" t="n">
-        <v>3.98</v>
+        <v>2.6</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="P33" t="n">
-        <v>2.08</v>
+        <v>4.12</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.43</v>
+        <v>2.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="P34" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.98</v>
+        <v>3.4</v>
       </c>
       <c r="O35" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>3.45</v>
+        <v>2.08</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.73</v>
+        <v>2.16</v>
       </c>
       <c r="O37" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="P37" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,13 +7721,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="O46" t="n">
         <v>2.7</v>
       </c>
       <c r="P46" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z46" t="n">
         <v>2.1</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,14 +7880,14 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.58</v>
+        <v>2.29</v>
       </c>
       <c r="O47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P47" t="n">
         <v>3.42</v>
       </c>
-      <c r="P47" t="n">
-        <v>5.74</v>
-      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
@@ -7913,16 +7913,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,13 +8039,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="O48" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="P48" t="n">
-        <v>3.35</v>
+        <v>5.74</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -8072,16 +8072,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.85</v>
+        <v>2.44</v>
       </c>
       <c r="O49" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>4.33</v>
+        <v>3.02</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P50" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V50" t="n">
         <v>1.8</v>
       </c>
-      <c r="O50" t="n">
+      <c r="W50" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB50" t="n">
         <v>3.2</v>
       </c>
-      <c r="P50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="O51" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="P51" t="n">
-        <v>5.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.67</v>
+        <v>2.44</v>
       </c>
       <c r="R51" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="S51" t="n">
-        <v>1.17</v>
+        <v>1.46</v>
       </c>
       <c r="T51" t="n">
-        <v>4.5</v>
+        <v>2.41</v>
       </c>
       <c r="U51" t="n">
-        <v>1.91</v>
+        <v>3.14</v>
       </c>
       <c r="V51" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="W51" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.06</v>
+        <v>1.38</v>
       </c>
       <c r="Z51" t="n">
-        <v>7.5</v>
+        <v>2.62</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.33</v>
+        <v>2.18</v>
       </c>
       <c r="AB51" t="n">
-        <v>3.2</v>
+        <v>1.58</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.85</v>
+        <v>4.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.85</v>
+        <v>1.18</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="AG51" t="n">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AK51" t="n">
-        <v>3.25</v>
+        <v>1.82</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,13 +8675,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.44</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P52" t="n">
-        <v>3.02</v>
+        <v>4.33</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,16 +8708,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,13 +8834,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="O53" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="P53" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8989,17 +8989,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9148,17 +9148,17 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,13 +9470,13 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="O57" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="P57" t="n">
-        <v>3.81</v>
+        <v>3.36</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -9503,16 +9503,16 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA57" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -9638,34 +9638,34 @@
         <v>2.55</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA58" t="n">
         <v>2.5</v>
@@ -9674,19 +9674,19 @@
         <v>1.5</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="O59" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="P59" t="n">
-        <v>3.36</v>
+        <v>3.81</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9821,16 +9821,16 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -9956,34 +9956,34 @@
         <v>3.3</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA60" t="n">
         <v>2.87</v>
@@ -9992,19 +9992,19 @@
         <v>1.4</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="O62" t="n">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="P62" t="n">
-        <v>3.57</v>
+        <v>4.53</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AC62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10420,17 +10420,17 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,16 +10463,16 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,64 +10583,64 @@
         </is>
       </c>
       <c r="N64" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O64" t="n">
+        <v>5</v>
+      </c>
+      <c r="P64" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R64" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S64" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC64" t="n">
         <v>2</v>
       </c>
-      <c r="O64" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P64" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" t="n">
-        <v>0</v>
-      </c>
-      <c r="W64" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>0</v>
-      </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10653,10 +10653,10 @@
         </is>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10738,68 +10738,68 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="O66" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="P66" t="n">
-        <v>4.53</v>
+        <v>3.57</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK66" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>
@@ -11069,55 +11069,55 @@
         <v>3.8</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -11228,55 +11228,55 @@
         <v>3.5</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11289,10 +11289,10 @@
         </is>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL68" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="O9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>3.03</v>
+        <v>3.47</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>2.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.8</v>
+        <v>2.77</v>
       </c>
       <c r="O15" t="n">
-        <v>4.27</v>
+        <v>3.45</v>
       </c>
       <c r="P15" t="n">
-        <v>3.46</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>8.6</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="O18" t="n">
-        <v>3.66</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>6.44</v>
+        <v>3.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>3.67</v>
       </c>
       <c r="P19" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.06</v>
+        <v>3.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="S19" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.41</v>
+        <v>2.96</v>
       </c>
       <c r="U19" t="n">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="V19" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.54</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="O20" t="n">
-        <v>4.28</v>
+        <v>3.41</v>
       </c>
       <c r="P20" t="n">
-        <v>5.58</v>
+        <v>2.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.01</v>
+        <v>2.29</v>
       </c>
       <c r="R20" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="U20" t="n">
-        <v>2.56</v>
+        <v>1.86</v>
       </c>
       <c r="V20" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.82</v>
+        <v>6.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.02</v>
+        <v>3.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.95</v>
+        <v>1.82</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.96</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.89</v>
+        <v>3.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.23</v>
+        <v>1.79</v>
       </c>
       <c r="O21" t="n">
-        <v>3.55</v>
+        <v>3.21</v>
       </c>
       <c r="P21" t="n">
-        <v>2.74</v>
+        <v>3.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>8.6</v>
+        <v>1.8</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>1.29</v>
+        <v>3.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,19 +4064,19 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -4097,31 +4097,31 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.87</v>
+        <v>2.17</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.87</v>
+        <v>2.43</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.15</v>
+        <v>4.33</v>
       </c>
       <c r="O24" t="n">
-        <v>3.67</v>
+        <v>4.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.11</v>
+        <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="R24" t="n">
-        <v>2.16</v>
+        <v>2.37</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="U24" t="n">
-        <v>2.59</v>
+        <v>2.08</v>
       </c>
       <c r="V24" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.05</v>
+        <v>2.17</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.27</v>
+        <v>2.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.39</v>
+        <v>1.15</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4382,43 +4382,43 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="O25" t="n">
-        <v>6.85</v>
+        <v>5.5</v>
       </c>
       <c r="P25" t="n">
-        <v>9.6</v>
+        <v>7.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA25" t="n">
         <v>1.3</v>
@@ -4427,19 +4427,19 @@
         <v>3.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>4.45</v>
+        <v>1.55</v>
       </c>
       <c r="O26" t="n">
-        <v>4.15</v>
+        <v>3.66</v>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>6.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>2.12</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="O27" t="n">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="P27" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.91</v>
       </c>
-      <c r="O28" t="n">
-        <v>3</v>
-      </c>
-      <c r="P28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="O29" t="n">
-        <v>3.69</v>
+        <v>4.28</v>
       </c>
       <c r="P29" t="n">
-        <v>3.3</v>
+        <v>5.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P31" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="O32" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="O33" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="P33" t="n">
-        <v>4.12</v>
+        <v>3.45</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6617,10 +6617,10 @@
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -6629,10 +6629,10 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -6641,31 +6641,31 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6776,34 +6776,34 @@
         <v>2.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA40" t="n">
         <v>1.8</v>
@@ -6812,19 +6812,19 @@
         <v>2</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="P41" t="n">
-        <v>4.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.81</v>
+        <v>2.17</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="O42" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7253,28 +7253,28 @@
         <v>2.26</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y43" t="n">
         <v>1.71</v>
@@ -7289,19 +7289,19 @@
         <v>1.3</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7571,28 +7571,28 @@
         <v>4.33</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y45" t="n">
         <v>1.68</v>
@@ -7607,19 +7607,19 @@
         <v>1.3</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="O46" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="P46" t="n">
-        <v>3.35</v>
+        <v>5.74</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,40 +7880,40 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="O47" t="n">
         <v>2.7</v>
       </c>
       <c r="P47" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z47" t="n">
         <v>2.1</v>
@@ -7925,19 +7925,19 @@
         <v>1.33</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.58</v>
+        <v>2.29</v>
       </c>
       <c r="O48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P48" t="n">
         <v>3.42</v>
       </c>
-      <c r="P48" t="n">
-        <v>5.74</v>
-      </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="P49" t="n">
-        <v>3.02</v>
+        <v>3.44</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="O50" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="P50" t="n">
-        <v>5.75</v>
+        <v>4.33</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.67</v>
+        <v>2.76</v>
       </c>
       <c r="R50" t="n">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="S50" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="T50" t="n">
-        <v>4.5</v>
+        <v>2.08</v>
       </c>
       <c r="U50" t="n">
-        <v>1.91</v>
+        <v>3.45</v>
       </c>
       <c r="V50" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="W50" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="Z50" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.33</v>
+        <v>2.87</v>
       </c>
       <c r="AB50" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.85</v>
+        <v>5.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.85</v>
+        <v>1.14</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="AG50" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AK50" t="n">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,17 +8671,17 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8708,16 +8708,16 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.3</v>
+        <v>1.36</v>
       </c>
       <c r="O53" t="n">
-        <v>3.03</v>
+        <v>4.8</v>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.65</v>
+        <v>3.2</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -9002,34 +9002,34 @@
         <v>4.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA54" t="n">
         <v>2.7</v>
@@ -9038,19 +9038,19 @@
         <v>1.44</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9148,68 +9148,68 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,65 +9311,65 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="O56" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
-        <v>3.44</v>
+        <v>3.02</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y56" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AG56" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z56" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
       <c r="AH56" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9479,28 +9479,28 @@
         <v>3.36</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y57" t="n">
         <v>1.57</v>
@@ -9515,19 +9515,19 @@
         <v>1.44</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,64 +9629,64 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="O58" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="P58" t="n">
-        <v>2.55</v>
+        <v>3.81</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC58" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="O59" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="P59" t="n">
-        <v>3.81</v>
+        <v>2.55</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -10115,34 +10115,34 @@
         <v>5</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA61" t="n">
         <v>1.7</v>
@@ -10151,19 +10151,19 @@
         <v>2.1</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10176,10 +10176,10 @@
         </is>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK61" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AL61" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10265,64 +10265,64 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="O62" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="P62" t="n">
-        <v>4.53</v>
+        <v>3.57</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10420,68 +10420,68 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10579,68 +10579,68 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10653,10 +10653,10 @@
         </is>
       </c>
       <c r="AJ64" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK64" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,64 +10742,64 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="O65" t="n">
-        <v>3.02</v>
+        <v>3.72</v>
       </c>
       <c r="P65" t="n">
-        <v>4.16</v>
+        <v>4.53</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AC65" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="AJ65" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="P66" t="n">
-        <v>3.57</v>
+        <v>4.16</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="R66" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="S66" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="T66" t="n">
-        <v>2.47</v>
+        <v>2.16</v>
       </c>
       <c r="U66" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="V66" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="W66" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X66" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AC66" t="n">
-        <v>3.78</v>
+        <v>4.6</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,64 +11060,64 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O67" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P67" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R67" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="S67" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="T67" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U67" t="n">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="V67" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="W67" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X67" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AC67" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="AJ67" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,64 +11219,64 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O68" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P68" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R68" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="S68" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="T68" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="U68" t="n">
-        <v>3.78</v>
+        <v>3.42</v>
       </c>
       <c r="V68" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W68" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X68" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AC68" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11289,10 +11289,10 @@
         </is>
       </c>
       <c r="AJ68" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK68" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL68" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P16" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.32</v>
+        <v>4.1</v>
       </c>
       <c r="R16" t="n">
-        <v>2.61</v>
+        <v>2.37</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U16" t="n">
         <v>2.08</v>
       </c>
       <c r="V16" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
         <v>1.47</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK16" t="n">
         <v>1.15</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>8.6</v>
+        <v>1.53</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>4.28</v>
       </c>
       <c r="P17" t="n">
-        <v>1.29</v>
+        <v>5.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.75</v>
+        <v>2.01</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U17" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="V17" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.28</v>
+        <v>2.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.04</v>
+        <v>2.39</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.91</v>
+        <v>1.26</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="P18" t="n">
-        <v>3.75</v>
+        <v>7.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>1.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.11</v>
+        <v>2.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.38</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.59</v>
+        <v>1.91</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.21</v>
       </c>
-      <c r="Z19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK19" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.89</v>
+        <v>3.15</v>
       </c>
       <c r="O20" t="n">
-        <v>3.41</v>
+        <v>3.67</v>
       </c>
       <c r="P20" t="n">
-        <v>2.81</v>
+        <v>2.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.29</v>
+        <v>3.38</v>
       </c>
       <c r="R20" t="n">
-        <v>2.75</v>
+        <v>2.16</v>
       </c>
       <c r="S20" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>4.5</v>
+        <v>2.96</v>
       </c>
       <c r="U20" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.86</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>3.14</v>
-      </c>
       <c r="AC20" t="n">
-        <v>1.82</v>
+        <v>3.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.96</v>
+        <v>1.32</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="O21" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>3.21</v>
+        <v>3.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>8.6</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>3.08</v>
+        <v>1.29</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.19</v>
+        <v>6.75</v>
       </c>
       <c r="R22" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="S22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="V22" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.15</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.13</v>
-      </c>
       <c r="Z22" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.69</v>
+        <v>1.83</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.94</v>
+        <v>1.04</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>2.74</v>
+        <v>1.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.75</v>
+        <v>4.32</v>
       </c>
       <c r="R23" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U23" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.2</v>
+        <v>5.65</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.43</v>
+        <v>2.14</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.21</v>
+        <v>2.2</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>4.33</v>
+        <v>1.8</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P24" t="n">
-        <v>1.48</v>
+        <v>3.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.1</v>
+        <v>2.19</v>
       </c>
       <c r="R24" t="n">
-        <v>2.37</v>
+        <v>2.64</v>
       </c>
       <c r="S24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T24" t="n">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="U24" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V24" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W24" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
         <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>2.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.26</v>
+        <v>2.23</v>
       </c>
       <c r="O25" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="P25" t="n">
-        <v>7.75</v>
+        <v>2.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.61</v>
+        <v>2.75</v>
       </c>
       <c r="R25" t="n">
-        <v>2.99</v>
+        <v>2.35</v>
       </c>
       <c r="S25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="V25" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.5</v>
+        <v>2.17</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.76</v>
+        <v>2.43</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.01</v>
+        <v>1.45</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AK25" t="n">
-        <v>3.6</v>
+        <v>1.46</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.55</v>
       </c>
-      <c r="O26" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="P26" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="AE26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.46</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="P28" t="n">
-        <v>2.82</v>
+        <v>6.44</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.44</v>
+        <v>2.03</v>
       </c>
       <c r="S28" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="T28" t="n">
-        <v>4.3</v>
+        <v>2.65</v>
       </c>
       <c r="U28" t="n">
-        <v>1.91</v>
+        <v>3.3</v>
       </c>
       <c r="V28" t="n">
-        <v>1.77</v>
+        <v>1.31</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.6</v>
+        <v>2.78</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.34</v>
+        <v>2.12</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.92</v>
+        <v>1.64</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.94</v>
+        <v>4.14</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.31</v>
+        <v>1.03</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.04</v>
+        <v>1.63</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="O29" t="n">
-        <v>4.28</v>
+        <v>3.41</v>
       </c>
       <c r="P29" t="n">
-        <v>5.58</v>
+        <v>2.81</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.01</v>
+        <v>2.29</v>
       </c>
       <c r="R29" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="S29" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T29" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="U29" t="n">
-        <v>2.56</v>
+        <v>1.86</v>
       </c>
       <c r="V29" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.82</v>
+        <v>6.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.02</v>
+        <v>3.14</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.95</v>
+        <v>1.82</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.96</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.8</v>
+        <v>1.31</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.89</v>
+        <v>3.2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>1.2</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.21</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="P33" t="n">
-        <v>3.45</v>
+        <v>4.12</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.73</v>
+        <v>1.98</v>
       </c>
       <c r="O34" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.85</v>
+        <v>2.73</v>
       </c>
       <c r="O36" t="n">
-        <v>3.52</v>
+        <v>2.98</v>
       </c>
       <c r="P36" t="n">
-        <v>4.12</v>
+        <v>2.76</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="O44" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="P44" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="O45" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="P45" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AC45" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="O46" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="P46" t="n">
-        <v>5.74</v>
+        <v>3.35</v>
       </c>
       <c r="Q46" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T46" t="n">
         <v>2.02</v>
       </c>
-      <c r="R46" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.42</v>
-      </c>
       <c r="U46" t="n">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="V46" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="W46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE46" t="n">
         <v>1.02</v>
       </c>
-      <c r="X46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1</v>
-      </c>
       <c r="AF46" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.6</v>
+        <v>1.46</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,40 +7880,40 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="O47" t="n">
         <v>2.7</v>
       </c>
       <c r="P47" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.34</v>
+        <v>2.82</v>
       </c>
       <c r="R47" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="S47" t="n">
         <v>1.7</v>
       </c>
       <c r="T47" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="U47" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="V47" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="W47" t="n">
         <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Z47" t="n">
         <v>2.1</v>
@@ -7925,19 +7925,19 @@
         <v>1.33</v>
       </c>
       <c r="AC47" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AE47" t="n">
         <v>1.02</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.29</v>
+        <v>1.58</v>
       </c>
       <c r="O48" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="P48" t="n">
-        <v>3.42</v>
+        <v>5.74</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.82</v>
+        <v>2.02</v>
       </c>
       <c r="R48" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="S48" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="T48" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="U48" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="V48" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X48" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>6.25</v>
+        <v>4.3</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,68 +8353,68 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,64 +8516,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O51" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P51" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="R51" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="S51" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="T51" t="n">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="U51" t="n">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="V51" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="W51" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X51" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE51" t="n">
         <v>1.03</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,68 +8671,68 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1.36</v>
+        <v>2.44</v>
       </c>
       <c r="O53" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
-        <v>5.75</v>
+        <v>3.02</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="R53" t="n">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="S53" t="n">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="T53" t="n">
-        <v>4.5</v>
+        <v>2.34</v>
       </c>
       <c r="U53" t="n">
-        <v>1.91</v>
+        <v>3.42</v>
       </c>
       <c r="V53" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="W53" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="X53" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE53" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y53" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AF53" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="AG53" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AK53" t="n">
-        <v>3.25</v>
+        <v>1.52</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,80 +8993,80 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="O54" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="P54" t="n">
-        <v>4.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.58</v>
+        <v>1.67</v>
       </c>
       <c r="R54" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="S54" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="T54" t="n">
-        <v>2.22</v>
+        <v>4.5</v>
       </c>
       <c r="U54" t="n">
-        <v>3.6</v>
+        <v>1.91</v>
       </c>
       <c r="V54" t="n">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="X54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54" t="n">
         <v>1.11</v>
       </c>
-      <c r="Y54" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AK54" t="n">
-        <v>1.83</v>
+        <v>3.25</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,80 +9152,80 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="O55" t="n">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="P55" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R55" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.9</v>
-      </c>
       <c r="S55" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T55" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="U55" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="V55" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W55" t="n">
         <v>1.03</v>
       </c>
       <c r="X55" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AG55" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK55" t="n">
         <v>1.82</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>1.24</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="P56" t="n">
-        <v>3.02</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>4.68</v>
       </c>
       <c r="R56" t="n">
         <v>1.9</v>
       </c>
       <c r="S56" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T56" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="U56" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="V56" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W56" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X56" t="n">
         <v>1.07</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.53</v>
+        <v>3.09</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AC56" t="n">
-        <v>4.55</v>
+        <v>3.58</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>1.34</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,64 +9629,64 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="P58" t="n">
-        <v>3.81</v>
+        <v>2.55</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="AA58" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="O59" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="P59" t="n">
-        <v>2.55</v>
+        <v>3.81</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC59" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10261,68 +10261,68 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="AJ62" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,64 +10424,64 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>3.72</v>
       </c>
       <c r="P63" t="n">
-        <v>6</v>
+        <v>4.53</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.87</v>
+        <v>2.1</v>
       </c>
       <c r="AC63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK63" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10579,68 +10579,68 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10653,10 +10653,10 @@
         </is>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,64 +10742,64 @@
         </is>
       </c>
       <c r="N65" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P65" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S65" t="n">
         <v>1.64</v>
       </c>
-      <c r="O65" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="P65" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB65" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O66" t="n">
+        <v>5</v>
+      </c>
+      <c r="P66" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC66" t="n">
         <v>2</v>
       </c>
-      <c r="O66" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P66" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S66" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U66" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X66" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AD66" t="n">
-        <v>1.13</v>
+        <v>1.8</v>
       </c>
       <c r="AE66" t="n">
-        <v>1</v>
+        <v>1.31</v>
       </c>
       <c r="AF66" t="n">
-        <v>2.02</v>
+        <v>1.52</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.66</v>
+        <v>2.88</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,64 +11060,64 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O67" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P67" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R67" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="S67" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="T67" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="U67" t="n">
-        <v>3.78</v>
+        <v>3.42</v>
       </c>
       <c r="V67" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W67" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X67" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AC67" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="AJ67" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,64 +11219,64 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O68" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P68" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R68" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="S68" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="T68" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U68" t="n">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="V68" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="W68" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X68" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AC68" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11289,10 +11289,10 @@
         </is>
       </c>
       <c r="AJ68" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK68" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AL68" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="P13" t="n">
-        <v>3.47</v>
+        <v>2.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.78</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.77</v>
+        <v>8.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>1.29</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>6.75</v>
       </c>
       <c r="R15" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.5</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4.33</v>
+        <v>1.26</v>
       </c>
       <c r="O16" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="P16" t="n">
-        <v>1.48</v>
+        <v>7.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.1</v>
+        <v>1.61</v>
       </c>
       <c r="R16" t="n">
-        <v>2.37</v>
+        <v>2.99</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U16" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="V16" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.17</v>
+        <v>1.76</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.65</v>
+        <v>2.01</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>2.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.15</v>
+        <v>3.6</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="O17" t="n">
-        <v>4.28</v>
+        <v>2.87</v>
       </c>
       <c r="P17" t="n">
-        <v>5.58</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.01</v>
+        <v>3.1</v>
       </c>
       <c r="R17" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="T17" t="n">
-        <v>3.08</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>2.56</v>
+        <v>3.45</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.82</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.76</v>
+        <v>2.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF17" t="n">
         <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.39</v>
+        <v>1.53</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.26</v>
+        <v>1.95</v>
       </c>
       <c r="O18" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>7.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="R18" t="n">
-        <v>2.99</v>
+        <v>2.44</v>
       </c>
       <c r="S18" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="V18" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="W18" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="X18" t="n">
         <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.3</v>
+        <v>3.04</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.95</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="P19" t="n">
-        <v>2.82</v>
+        <v>2.11</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>3.38</v>
       </c>
       <c r="R19" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="S19" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>4.3</v>
+        <v>2.96</v>
       </c>
       <c r="U19" t="n">
-        <v>1.91</v>
+        <v>2.59</v>
       </c>
       <c r="V19" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.92</v>
+        <v>1.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.94</v>
+        <v>3.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.04</v>
+        <v>2.14</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.11</v>
+        <v>3.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.38</v>
+        <v>2.19</v>
       </c>
       <c r="R20" t="n">
-        <v>2.16</v>
+        <v>2.64</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T20" t="n">
-        <v>2.96</v>
+        <v>3.96</v>
       </c>
       <c r="U20" t="n">
-        <v>2.59</v>
+        <v>2.05</v>
       </c>
       <c r="V20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.41</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG20" t="n">
-        <v>2.14</v>
+        <v>2.69</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.39</v>
+        <v>1.94</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.91</v>
+        <v>2.77</v>
       </c>
       <c r="O21" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P21" t="n">
-        <v>3.75</v>
+        <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="P22" t="n">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="Q22" t="n">
-        <v>6.75</v>
+        <v>4.32</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U22" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V22" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK22" t="n">
         <v>1.15</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.04</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="O23" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.32</v>
+        <v>4.1</v>
       </c>
       <c r="R23" t="n">
-        <v>2.61</v>
+        <v>2.37</v>
       </c>
       <c r="S23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T23" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U23" t="n">
         <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
         <v>1.47</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK23" t="n">
         <v>1.15</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="O24" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="P24" t="n">
-        <v>3.08</v>
+        <v>6.44</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.64</v>
+        <v>2.03</v>
       </c>
       <c r="S24" t="n">
-        <v>1.18</v>
+        <v>1.46</v>
       </c>
       <c r="T24" t="n">
-        <v>3.96</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="W24" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.8</v>
+        <v>2.78</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.37</v>
+        <v>2.11</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.08</v>
+        <v>3.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.69</v>
+        <v>1.63</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>1.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,19 +4382,19 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="O25" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.74</v>
+        <v>3.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4415,31 +4415,31 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9</v>
+        <v>3.41</v>
       </c>
       <c r="P27" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.06</v>
+        <v>2.29</v>
       </c>
       <c r="R27" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="S27" t="n">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="T27" t="n">
-        <v>2.41</v>
+        <v>4.5</v>
       </c>
       <c r="U27" t="n">
-        <v>3.25</v>
+        <v>1.86</v>
       </c>
       <c r="V27" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>1.31</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.78</v>
+        <v>3.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O28" t="n">
-        <v>3.66</v>
+        <v>4.28</v>
       </c>
       <c r="P28" t="n">
-        <v>6.44</v>
+        <v>5.58</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="R28" t="n">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="S28" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="U28" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="V28" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="W28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.02</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.78</v>
+        <v>3.82</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.14</v>
+        <v>2.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="O29" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="P29" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="S29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="V29" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.14</v>
+        <v>2.17</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.82</v>
+        <v>2.43</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.96</v>
+        <v>1.45</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.21</v>
+        <v>3.4</v>
       </c>
       <c r="O30" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>1.98</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>2.08</v>
+        <v>3.45</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P34" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="O46" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="P46" t="n">
-        <v>3.35</v>
+        <v>5.74</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.34</v>
+        <v>2.02</v>
       </c>
       <c r="R46" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="S46" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="T46" t="n">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="U46" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC46" t="n">
         <v>4.3</v>
       </c>
-      <c r="V46" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AD46" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.46</v>
+        <v>2.6</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="O48" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="P48" t="n">
-        <v>5.74</v>
+        <v>3.35</v>
       </c>
       <c r="Q48" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T48" t="n">
         <v>2.02</v>
       </c>
-      <c r="R48" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.42</v>
-      </c>
       <c r="U48" t="n">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="V48" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="W48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE48" t="n">
         <v>1.02</v>
       </c>
-      <c r="X48" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1</v>
-      </c>
       <c r="AF48" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.6</v>
+        <v>1.46</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,65 +8198,65 @@
         </is>
       </c>
       <c r="N49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P49" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG49" t="n">
         <v>2.3</v>
       </c>
-      <c r="O49" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="P49" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,68 +8353,68 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,68 +8512,68 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="P53" t="n">
-        <v>3.02</v>
+        <v>3.44</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC53" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="O54" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="P54" t="n">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.67</v>
+        <v>2.58</v>
       </c>
       <c r="R54" t="n">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="S54" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="T54" t="n">
-        <v>4.5</v>
+        <v>2.22</v>
       </c>
       <c r="U54" t="n">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="V54" t="n">
-        <v>1.8</v>
+        <v>1.19</v>
       </c>
       <c r="W54" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="X54" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="Z54" t="n">
-        <v>7.5</v>
+        <v>2.33</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="AB54" t="n">
-        <v>3.2</v>
+        <v>1.44</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.85</v>
+        <v>1.13</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="AG54" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AK54" t="n">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="O55" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="P55" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.44</v>
+        <v>4.68</v>
       </c>
       <c r="R55" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S55" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T55" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="U55" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="V55" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W55" t="n">
         <v>1.03</v>
       </c>
       <c r="X55" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.62</v>
+        <v>3.09</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC55" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,80 +9311,80 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="O56" t="n">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="P56" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.9</v>
-      </c>
       <c r="S56" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T56" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="U56" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="V56" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W56" t="n">
         <v>1.03</v>
       </c>
       <c r="X56" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC56" t="n">
-        <v>3.58</v>
+        <v>4.4</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AG56" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK56" t="n">
         <v>1.82</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>1.24</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,65 +9470,65 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="O57" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="P57" t="n">
-        <v>3.36</v>
+        <v>2.55</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG57" t="n">
         <v>1.68</v>
       </c>
-      <c r="S57" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U57" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X57" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AH57" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,64 +9629,64 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="O58" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="P58" t="n">
-        <v>2.55</v>
+        <v>3.36</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="R58" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="S58" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="T58" t="n">
-        <v>2.31</v>
+        <v>2.04</v>
       </c>
       <c r="U58" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="V58" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="W58" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X58" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC58" t="n">
-        <v>4.55</v>
+        <v>5.22</v>
       </c>
       <c r="AD58" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,64 +10424,64 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.64</v>
+        <v>2.08</v>
       </c>
       <c r="O63" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="P63" t="n">
-        <v>4.53</v>
+        <v>3.57</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,64 +10583,64 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="O64" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>3.57</v>
+        <v>6</v>
       </c>
       <c r="Q64" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R64" t="n">
         <v>2.7</v>
       </c>
-      <c r="R64" t="n">
-        <v>2.1</v>
-      </c>
       <c r="S64" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="W64" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA64" t="n">
         <v>1.4</v>
       </c>
-      <c r="T64" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U64" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V64" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W64" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X64" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y64" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AB64" t="n">
-        <v>1.6</v>
+        <v>2.87</v>
       </c>
       <c r="AC64" t="n">
-        <v>3.78</v>
+        <v>2</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="AG64" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10653,10 +10653,10 @@
         </is>
       </c>
       <c r="AJ64" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AK64" t="n">
-        <v>1.69</v>
+        <v>2.88</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,64 +10742,64 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="O65" t="n">
-        <v>3.02</v>
+        <v>3.72</v>
       </c>
       <c r="P65" t="n">
-        <v>4.16</v>
+        <v>4.53</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AC65" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10812,10 +10812,10 @@
         </is>
       </c>
       <c r="AJ65" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,80 +10901,80 @@
         </is>
       </c>
       <c r="N66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P66" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66" t="n">
         <v>1.33</v>
       </c>
-      <c r="O66" t="n">
-        <v>5</v>
-      </c>
-      <c r="P66" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R66" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S66" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T66" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W66" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X66" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AK66" t="n">
-        <v>2.88</v>
+        <v>1.66</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,19 +2792,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>8.6</v>
+        <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.29</v>
+        <v>3.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -2813,10 +2813,10 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2825,31 +2825,31 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.25</v>
       </c>
-      <c r="O17" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AC17" t="n">
-        <v>4.1</v>
+        <v>2.28</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.53</v>
+        <v>1.04</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.95</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="P18" t="n">
-        <v>2.82</v>
+        <v>2.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.38</v>
+        <v>3.38</v>
       </c>
       <c r="R18" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="S18" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>4.3</v>
+        <v>2.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.91</v>
+        <v>2.59</v>
       </c>
       <c r="V18" t="n">
-        <v>1.77</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.34</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.92</v>
+        <v>1.86</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.94</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.04</v>
+        <v>2.14</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>1.53</v>
       </c>
       <c r="O19" t="n">
-        <v>3.67</v>
+        <v>4.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.11</v>
+        <v>5.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.38</v>
+        <v>2.01</v>
       </c>
       <c r="R19" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="S19" t="n">
         <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="U19" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
         <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
         <v>1.09</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.39</v>
+        <v>2.39</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>2.87</v>
       </c>
       <c r="P20" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.19</v>
+        <v>3.02</v>
       </c>
       <c r="R20" t="n">
-        <v>2.64</v>
+        <v>1.92</v>
       </c>
       <c r="S20" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="T20" t="n">
-        <v>3.96</v>
+        <v>2.55</v>
       </c>
       <c r="U20" t="n">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.71</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.8</v>
+        <v>2.62</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.37</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.66</v>
+        <v>1.59</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.69</v>
+        <v>1.79</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.94</v>
+        <v>1.54</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.77</v>
+        <v>1.79</v>
       </c>
       <c r="O21" t="n">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="P21" t="n">
-        <v>2.36</v>
+        <v>3.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="R21" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="U21" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.92</v>
+        <v>4.63</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.66</v>
+        <v>2.34</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.4</v>
+        <v>1.92</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>4.33</v>
+        <v>1.55</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>3.66</v>
       </c>
       <c r="P23" t="n">
-        <v>1.48</v>
+        <v>6.44</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="R23" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="S23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.2</v>
       </c>
-      <c r="T23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="AK23" t="n">
         <v>2.25</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>6.44</v>
+        <v>2.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="R24" t="n">
-        <v>2.03</v>
+        <v>2.44</v>
       </c>
       <c r="S24" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>4.3</v>
       </c>
       <c r="U24" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="V24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.31</v>
       </c>
-      <c r="W24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF24" t="n">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.63</v>
+        <v>3.04</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.91</v>
+        <v>2.77</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>3.75</v>
+        <v>2.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,61 +4541,61 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.79</v>
+        <v>4.33</v>
       </c>
       <c r="O26" t="n">
-        <v>3.21</v>
+        <v>4.1</v>
       </c>
       <c r="P26" t="n">
-        <v>3.21</v>
+        <v>1.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.31</v>
+        <v>4.1</v>
       </c>
       <c r="R26" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="S26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T26" t="n">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="U26" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="V26" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.63</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG26" t="n">
         <v>2.4</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.24</v>
+        <v>2.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.92</v>
+        <v>1.15</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="O27" t="n">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="P27" t="n">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="R27" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="S27" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T27" t="n">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="U27" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="V27" t="n">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.95</v>
+        <v>5.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.14</v>
+        <v>2.66</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>1.2</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.53</v>
+        <v>2.23</v>
       </c>
       <c r="O28" t="n">
-        <v>4.28</v>
+        <v>3.55</v>
       </c>
       <c r="P28" t="n">
-        <v>5.58</v>
+        <v>2.74</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.01</v>
+        <v>2.75</v>
       </c>
       <c r="R28" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="S28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.56</v>
+        <v>2.23</v>
       </c>
       <c r="V28" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.39</v>
+        <v>1.46</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.23</v>
+        <v>1.89</v>
       </c>
       <c r="O29" t="n">
-        <v>3.55</v>
+        <v>3.41</v>
       </c>
       <c r="P29" t="n">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="Q29" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R29" t="n">
         <v>2.75</v>
       </c>
-      <c r="R29" t="n">
-        <v>2.35</v>
-      </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U29" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="V29" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.2</v>
+        <v>6.95</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.17</v>
+        <v>3.14</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.43</v>
+        <v>1.82</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.45</v>
+        <v>1.96</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.46</v>
+        <v>1.8</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P30" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="O34" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="P34" t="n">
-        <v>2.9</v>
+        <v>4.12</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.85</v>
+        <v>3.4</v>
       </c>
       <c r="O37" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>4.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -7244,49 +7244,49 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.53</v>
+        <v>2.9</v>
       </c>
       <c r="O43" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="P43" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="Q43" t="n">
         <v>4.34</v>
       </c>
       <c r="R43" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="S43" t="n">
         <v>1.75</v>
       </c>
       <c r="T43" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="U43" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="W43" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
         <v>1.16</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
         <v>6.3</v>
@@ -7298,7 +7298,7 @@
         <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AG43" t="n">
         <v>1.49</v>
@@ -7412,7 +7412,7 @@
         <v>4.33</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R44" t="n">
         <v>1.71</v>
@@ -7421,43 +7421,43 @@
         <v>1.74</v>
       </c>
       <c r="T44" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="U44" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W44" t="n">
         <v>1.02</v>
       </c>
       <c r="X44" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AC44" t="n">
         <v>5.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE44" t="n">
         <v>1.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="AG44" t="n">
         <v>1.48</v>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AK44" t="n">
         <v>1.73</v>
@@ -7565,10 +7565,10 @@
         <v>1.82</v>
       </c>
       <c r="O45" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P45" t="n">
-        <v>4.5</v>
+        <v>4.74</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7721,58 +7721,58 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="O46" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="P46" t="n">
-        <v>5.74</v>
+        <v>6.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S46" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T46" t="n">
         <v>2.42</v>
       </c>
       <c r="U46" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="V46" t="n">
         <v>1.23</v>
       </c>
       <c r="W46" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X46" t="n">
         <v>1.04</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z46" t="n">
         <v>2.46</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="AD46" t="n">
         <v>1.16</v>
       </c>
       <c r="AE46" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF46" t="n">
         <v>2.75</v>
@@ -7794,7 +7794,7 @@
         <v>1.19</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="O47" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="P47" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.82</v>
+        <v>3.34</v>
       </c>
       <c r="R47" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="S47" t="n">
         <v>1.7</v>
       </c>
       <c r="T47" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="U47" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="V47" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W47" t="n">
         <v>1.03</v>
       </c>
       <c r="X47" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AA47" t="n">
         <v>3.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC47" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AE47" t="n">
         <v>1.02</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="O48" t="n">
         <v>2.7</v>
       </c>
       <c r="P48" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.34</v>
+        <v>2.82</v>
       </c>
       <c r="R48" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="S48" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="T48" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U48" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="V48" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W48" t="n">
         <v>1.03</v>
       </c>
       <c r="X48" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AB48" t="n">
         <v>1.33</v>
       </c>
       <c r="AC48" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AE48" t="n">
         <v>1.02</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="O49" t="n">
-        <v>4.8</v>
+        <v>2.93</v>
       </c>
       <c r="P49" t="n">
-        <v>5.75</v>
+        <v>3.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.67</v>
+        <v>2.76</v>
       </c>
       <c r="R49" t="n">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="S49" t="n">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="T49" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="U49" t="n">
-        <v>1.91</v>
+        <v>3.75</v>
       </c>
       <c r="V49" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="W49" t="n">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="X49" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.06</v>
+        <v>1.56</v>
       </c>
       <c r="Z49" t="n">
-        <v>7.5</v>
+        <v>2.27</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.33</v>
+        <v>2.69</v>
       </c>
       <c r="AB49" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.85</v>
+        <v>5.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.85</v>
+        <v>1.12</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.36</v>
+        <v>1.03</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.5</v>
+        <v>2.32</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="AK49" t="n">
-        <v>3.25</v>
+        <v>1.75</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O50" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="P50" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AC50" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,68 +8512,68 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,64 +8675,64 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O52" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P52" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="R52" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="S52" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="T52" t="n">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="U52" t="n">
-        <v>3.45</v>
+        <v>3.14</v>
       </c>
       <c r="V52" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W52" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X52" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.87</v>
+        <v>2.18</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AC52" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE52" t="n">
         <v>1.03</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="O53" t="n">
-        <v>2.67</v>
+        <v>3.03</v>
       </c>
       <c r="P53" t="n">
-        <v>3.44</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="Z53" t="n">
-        <v>2</v>
+        <v>3.09</v>
       </c>
       <c r="AA53" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8993,40 +8993,40 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="O54" t="n">
         <v>3.05</v>
       </c>
       <c r="P54" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="R54" t="n">
         <v>1.83</v>
       </c>
       <c r="S54" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="T54" t="n">
         <v>2.22</v>
       </c>
       <c r="U54" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="V54" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W54" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X54" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z54" t="n">
         <v>2.33</v>
@@ -9035,13 +9035,13 @@
         <v>2.7</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AC54" t="n">
         <v>5</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AE54" t="n">
         <v>1.03</v>
@@ -9050,7 +9050,7 @@
         <v>2.32</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9148,68 +9148,68 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="O56" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P56" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S56" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AB56" t="n">
         <v>1.46</v>
       </c>
-      <c r="T56" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U56" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AC56" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,64 +9470,64 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O57" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="P57" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="R57" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="S57" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="T57" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="U57" t="n">
         <v>3.75</v>
       </c>
       <c r="V57" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W57" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X57" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y57" t="n">
         <v>1.49</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AC57" t="n">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="AD57" t="n">
         <v>1.13</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,65 +9629,65 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="O58" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="P58" t="n">
-        <v>3.36</v>
+        <v>2.55</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG58" t="n">
         <v>1.68</v>
       </c>
-      <c r="S58" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T58" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U58" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X58" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AH58" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="O59" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="P59" t="n">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -9947,28 +9947,28 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O60" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="P60" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="R60" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="S60" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="T60" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="U60" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="V60" t="n">
         <v>1.19</v>
@@ -9986,25 +9986,25 @@
         <v>2.31</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC60" t="n">
-        <v>6.5</v>
+        <v>6.07</v>
       </c>
       <c r="AD60" t="n">
         <v>1.08</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF60" t="n">
         <v>2.22</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -10261,68 +10261,68 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10424,64 +10424,64 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="O63" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>3.57</v>
+        <v>6</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="R63" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="S63" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="T63" t="n">
-        <v>2.47</v>
+        <v>4.3</v>
       </c>
       <c r="U63" t="n">
-        <v>3.05</v>
+        <v>1.91</v>
       </c>
       <c r="V63" t="n">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="W63" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X63" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.15</v>
+        <v>1.34</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.6</v>
+        <v>2.78</v>
       </c>
       <c r="AC63" t="n">
-        <v>3.78</v>
+        <v>1.92</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.2</v>
+        <v>1.79</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.03</v>
+        <v>1.31</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.69</v>
+        <v>2.88</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10579,68 +10579,68 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10653,10 +10653,10 @@
         </is>
       </c>
       <c r="AJ64" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK64" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,80 +10742,80 @@
         </is>
       </c>
       <c r="N65" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P65" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S65" t="n">
         <v>1.64</v>
       </c>
-      <c r="O65" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="P65" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA65" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK65" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>0</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="O66" t="n">
-        <v>3.02</v>
+        <v>3.72</v>
       </c>
       <c r="P66" t="n">
-        <v>4.16</v>
+        <v>4.53</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="AC66" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,64 +11060,64 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O67" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P67" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R67" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="S67" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="T67" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="U67" t="n">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="V67" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="W67" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X67" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AC67" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="AJ67" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,64 +11219,64 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O68" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P68" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R68" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="S68" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="T68" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="U68" t="n">
-        <v>3.78</v>
+        <v>3.42</v>
       </c>
       <c r="V68" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="W68" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X68" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AC68" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11289,10 +11289,10 @@
         </is>
       </c>
       <c r="AJ68" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK68" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL68" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.93</v>
+        <v>3.41</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>2.03</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1370,10 +1370,10 @@
         <v>1.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.41</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
         <v>1.33</v>
@@ -1400,13 +1400,13 @@
         <v>3.42</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AB6" t="n">
         <v>1.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD6" t="n">
         <v>1.32</v>
@@ -1415,10 +1415,10 @@
         <v>1.09</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="O8" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="P8" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
-        <v>2.78</v>
+        <v>3.47</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>2.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.91</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="P15" t="n">
-        <v>3.75</v>
+        <v>1.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.26</v>
+        <v>1.95</v>
       </c>
       <c r="O16" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="P16" t="n">
-        <v>7.75</v>
+        <v>3.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="W16" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.75</v>
+        <v>6.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>3.04</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>8.6</v>
+        <v>1.95</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>1.29</v>
+        <v>3.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>1.71</v>
       </c>
       <c r="O18" t="n">
-        <v>3.67</v>
+        <v>4.05</v>
       </c>
       <c r="P18" t="n">
-        <v>2.11</v>
+        <v>3.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.38</v>
+        <v>2.22</v>
       </c>
       <c r="R18" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="S18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.3</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V18" t="n">
+      <c r="AF18" t="n">
         <v>1.41</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG18" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.39</v>
+        <v>1.95</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.53</v>
-      </c>
-      <c r="O19" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="P19" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.39</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>3.88</v>
       </c>
       <c r="O20" t="n">
-        <v>2.87</v>
+        <v>4.4</v>
       </c>
       <c r="P20" t="n">
-        <v>3.1</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.92</v>
+        <v>2.61</v>
       </c>
       <c r="S20" t="n">
-        <v>1.51</v>
+        <v>1.16</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="U20" t="n">
-        <v>3.4</v>
+        <v>2.08</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.62</v>
+        <v>5.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.59</v>
+        <v>2.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.1</v>
+        <v>2.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.16</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.92</v>
+        <v>1.46</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.79</v>
+        <v>2.53</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.33</v>
+        <v>2.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,80 +3746,80 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.79</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>3.21</v>
+        <v>3.67</v>
       </c>
       <c r="P21" t="n">
-        <v>3.21</v>
+        <v>2.11</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="S21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.25</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.92</v>
+        <v>1.39</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>2.59</v>
       </c>
       <c r="O22" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.64</v>
+        <v>2.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.32</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2.61</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T22" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="U22" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.65</v>
+        <v>4.27</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.14</v>
+        <v>2.52</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.55</v>
+        <v>1.24</v>
       </c>
       <c r="O23" t="n">
-        <v>3.66</v>
+        <v>6</v>
       </c>
       <c r="P23" t="n">
-        <v>6.44</v>
+        <v>7.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="S23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.45</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>1.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="R24" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="S24" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="T24" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="V24" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.92</v>
+        <v>2.17</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.94</v>
+        <v>2.43</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.04</v>
+        <v>2.4</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>1.21</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,80 +4382,80 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.77</v>
+        <v>1.53</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>4.28</v>
       </c>
       <c r="P25" t="n">
-        <v>2.36</v>
+        <v>5.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>2.01</v>
       </c>
       <c r="R25" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="S25" t="n">
         <v>1.3</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.08</v>
       </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>2.17</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>4.33</v>
+        <v>1.86</v>
       </c>
       <c r="O26" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P26" t="n">
-        <v>1.48</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.1</v>
+        <v>2.29</v>
       </c>
       <c r="R26" t="n">
-        <v>2.37</v>
+        <v>2.7</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T26" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="U26" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="V26" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.15</v>
+        <v>1.8</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.8</v>
+        <v>8.6</v>
       </c>
       <c r="O27" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>3.08</v>
+        <v>1.29</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.19</v>
+        <v>6.75</v>
       </c>
       <c r="R27" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="S27" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T27" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="V27" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.69</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.2</v>
+        <v>2.88</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.94</v>
+        <v>1.05</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.23</v>
+        <v>1.82</v>
       </c>
       <c r="O28" t="n">
-        <v>3.55</v>
+        <v>3.76</v>
       </c>
       <c r="P28" t="n">
-        <v>2.74</v>
+        <v>3.87</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="R28" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="U28" t="n">
         <v>2.23</v>
       </c>
       <c r="V28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF28" t="n">
         <v>1.5</v>
       </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AG28" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="O29" t="n">
-        <v>3.41</v>
+        <v>3.66</v>
       </c>
       <c r="P29" t="n">
-        <v>2.81</v>
+        <v>6.44</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="S29" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="T29" t="n">
-        <v>4.5</v>
+        <v>2.53</v>
       </c>
       <c r="U29" t="n">
-        <v>1.86</v>
+        <v>3.2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.87</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="Z29" t="n">
-        <v>6.95</v>
+        <v>2.78</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.14</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.82</v>
+        <v>4.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.96</v>
+        <v>1.19</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.38</v>
+        <v>1.03</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.31</v>
+        <v>2.15</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.2</v>
+        <v>1.63</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.98</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>3.45</v>
+        <v>2.08</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,13 +5654,13 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="O34" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="P34" t="n">
-        <v>4.12</v>
+        <v>2.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,22 +6089,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.73</v>
+        <v>1.98</v>
       </c>
       <c r="O36" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="P36" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>3.4</v>
+        <v>1.84</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="P37" t="n">
-        <v>2.08</v>
+        <v>4.17</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6617,28 +6617,28 @@
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
         <v>2.4</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U39" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V39" t="n">
         <v>1.5</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39" t="n">
         <v>1.17</v>
@@ -6659,7 +6659,7 @@
         <v>1.44</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF39" t="n">
         <v>1.62</v>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="O40" t="n">
         <v>3.6</v>
@@ -6776,22 +6776,22 @@
         <v>2.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S40" t="n">
         <v>1.32</v>
       </c>
       <c r="T40" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="U40" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V40" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W40" t="n">
         <v>1.11</v>
@@ -6800,31 +6800,31 @@
         <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA40" t="n">
         <v>1.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AD40" t="n">
         <v>1.35</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF40" t="n">
         <v>1.61</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6926,25 +6926,25 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="O41" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="P41" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="R41" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S41" t="n">
         <v>1.2</v>
       </c>
       <c r="T41" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="U41" t="n">
         <v>2.12</v>
@@ -6953,28 +6953,28 @@
         <v>1.66</v>
       </c>
       <c r="W41" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z41" t="n">
-        <v>5.35</v>
+        <v>5.09</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AC41" t="n">
         <v>2.17</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE41" t="n">
         <v>1.27</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7085,31 +7085,31 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="O42" t="n">
-        <v>4.3</v>
+        <v>3.92</v>
       </c>
       <c r="P42" t="n">
-        <v>4.08</v>
+        <v>3.72</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R42" t="n">
         <v>2.62</v>
       </c>
       <c r="S42" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T42" t="n">
         <v>4.25</v>
       </c>
       <c r="U42" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="V42" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W42" t="n">
         <v>1.21</v>
@@ -7118,7 +7118,7 @@
         <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z42" t="n">
         <v>6.15</v>
@@ -7130,10 +7130,10 @@
         <v>3</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AE42" t="n">
         <v>1.33</v>
@@ -7253,16 +7253,16 @@
         <v>2.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.34</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="S43" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="T43" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="U43" t="n">
         <v>4.25</v>
@@ -7277,10 +7277,10 @@
         <v>1.16</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
         <v>3.08</v>
@@ -7298,10 +7298,10 @@
         <v>1.02</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="P44" t="n">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AC44" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="O45" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P45" t="n">
-        <v>4.74</v>
+        <v>4.33</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.4</v>
+        <v>2.29</v>
       </c>
       <c r="O46" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="P46" t="n">
-        <v>6.7</v>
+        <v>3.42</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="R46" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="S46" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="T46" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="U46" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="V46" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="W46" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.46</v>
+        <v>2.07</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7883,7 +7883,7 @@
         <v>2.31</v>
       </c>
       <c r="O47" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="P47" t="n">
         <v>3.05</v>
@@ -7919,7 +7919,7 @@
         <v>2.09</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="AB47" t="n">
         <v>1.29</v>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.29</v>
+        <v>1.37</v>
       </c>
       <c r="O48" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="P48" t="n">
-        <v>3.42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.82</v>
+        <v>1.95</v>
       </c>
       <c r="R48" t="n">
-        <v>1.74</v>
+        <v>1.99</v>
       </c>
       <c r="S48" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="T48" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="U48" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="V48" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="W48" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X48" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.04</v>
+        <v>2.32</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AC48" t="n">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AE48" t="n">
         <v>1.02</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.67</v>
+        <v>2.6</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.98</v>
+        <v>3.13</v>
       </c>
       <c r="O49" t="n">
-        <v>2.93</v>
+        <v>3.13</v>
       </c>
       <c r="P49" t="n">
-        <v>3.65</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.76</v>
+        <v>4.68</v>
       </c>
       <c r="R49" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="S49" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="T49" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U49" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="V49" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W49" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X49" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.27</v>
+        <v>3.05</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.69</v>
+        <v>2.17</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AC49" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.32</v>
+        <v>1.88</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -8390,16 +8390,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8516,80 +8516,80 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.33</v>
+        <v>2.41</v>
       </c>
       <c r="O51" t="n">
-        <v>5.58</v>
+        <v>3</v>
       </c>
       <c r="P51" t="n">
-        <v>7.22</v>
+        <v>2.75</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="R51" t="n">
-        <v>2.85</v>
+        <v>1.91</v>
       </c>
       <c r="S51" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="T51" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="U51" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="V51" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="W51" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="X51" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.06</v>
+        <v>1.49</v>
       </c>
       <c r="Z51" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.29</v>
+        <v>2.4</v>
       </c>
       <c r="AB51" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.85</v>
+        <v>4.5</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AE51" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF51" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK51" t="n">
-        <v>2.75</v>
+        <v>1.54</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,64 +8675,64 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O52" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="P52" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="R52" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S52" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="T52" t="n">
-        <v>2.41</v>
+        <v>2.08</v>
       </c>
       <c r="U52" t="n">
-        <v>3.14</v>
+        <v>3.7</v>
       </c>
       <c r="V52" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X52" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.18</v>
+        <v>2.87</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AC52" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE52" t="n">
         <v>1.03</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="O53" t="n">
-        <v>3.03</v>
+        <v>2.63</v>
       </c>
       <c r="P53" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z53" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S53" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U53" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V53" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>3.09</v>
-      </c>
       <c r="AA53" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AC53" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD53" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8993,7 +8993,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="O54" t="n">
         <v>3.05</v>
@@ -9002,22 +9002,22 @@
         <v>3.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="R54" t="n">
         <v>1.83</v>
       </c>
       <c r="S54" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="T54" t="n">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="U54" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="V54" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W54" t="n">
         <v>1.01</v>
@@ -9026,22 +9026,22 @@
         <v>1.07</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z54" t="n">
         <v>2.33</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AC54" t="n">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE54" t="n">
         <v>1.03</v>
@@ -9050,7 +9050,7 @@
         <v>2.32</v>
       </c>
       <c r="AG54" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9148,68 +9148,68 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>2.37</v>
+        <v>1.33</v>
       </c>
       <c r="O56" t="n">
-        <v>2.8</v>
+        <v>5.58</v>
       </c>
       <c r="P56" t="n">
-        <v>2.9</v>
+        <v>7.22</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="R56" t="n">
-        <v>1.91</v>
+        <v>2.85</v>
       </c>
       <c r="S56" t="n">
-        <v>1.52</v>
+        <v>1.14</v>
       </c>
       <c r="T56" t="n">
-        <v>2.34</v>
+        <v>4.3</v>
       </c>
       <c r="U56" t="n">
-        <v>3.42</v>
+        <v>1.8</v>
       </c>
       <c r="V56" t="n">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="W56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X56" t="n">
         <v>1.01</v>
       </c>
-      <c r="X56" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y56" t="n">
-        <v>1.49</v>
+        <v>1.06</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.53</v>
+        <v>7.5</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.39</v>
+        <v>1.29</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.46</v>
+        <v>3.3</v>
       </c>
       <c r="AC56" t="n">
-        <v>4.55</v>
+        <v>1.85</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.13</v>
+        <v>1.85</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9438,12 +9438,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9470,64 +9470,64 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="O57" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P57" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC57" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="AJ57" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -9638,16 +9638,16 @@
         <v>2.55</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R58" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="S58" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="T58" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="U58" t="n">
         <v>3.75</v>
@@ -9659,22 +9659,22 @@
         <v>1.02</v>
       </c>
       <c r="X58" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AB58" t="n">
         <v>1.5</v>
       </c>
       <c r="AC58" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="AD58" t="n">
         <v>1.13</v>
@@ -9702,7 +9702,7 @@
         <v>1.31</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="O59" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="P59" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U59" t="n">
         <v>3.75</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="AA59" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -9947,64 +9947,64 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O60" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P60" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="R60" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S60" t="n">
         <v>1.62</v>
       </c>
       <c r="T60" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="U60" t="n">
         <v>4</v>
       </c>
       <c r="V60" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W60" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X60" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="Z60" t="n">
         <v>2.31</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC60" t="n">
-        <v>6.07</v>
+        <v>6</v>
       </c>
       <c r="AD60" t="n">
         <v>1.08</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF60" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="AJ60" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -10106,64 +10106,64 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="O61" t="n">
-        <v>3.83</v>
+        <v>4.05</v>
       </c>
       <c r="P61" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="R61" t="n">
         <v>2.29</v>
       </c>
       <c r="S61" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T61" t="n">
         <v>3.1</v>
       </c>
       <c r="U61" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V61" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W61" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X61" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z61" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AA61" t="n">
         <v>1.7</v>
       </c>
       <c r="AB61" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC61" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AD61" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG61" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10176,10 +10176,10 @@
         </is>
       </c>
       <c r="AJ61" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AK61" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL61" t="n">
         <v>0</v>
@@ -10274,19 +10274,19 @@
         <v>3.57</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R62" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="S62" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T62" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="U62" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V62" t="n">
         <v>1.29</v>
@@ -10295,31 +10295,31 @@
         <v>1.03</v>
       </c>
       <c r="X62" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y62" t="n">
         <v>1.39</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC62" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG62" t="n">
         <v>1.75</v>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="AJ62" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10420,68 +10420,68 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10494,10 +10494,10 @@
         </is>
       </c>
       <c r="AJ63" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK63" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10579,17 +10579,17 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC64" t="n">
         <v>0</v>
@@ -10742,10 +10742,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1.98</v>
+        <v>2.14</v>
       </c>
       <c r="O65" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="P65" t="n">
         <v>3.6</v>
@@ -10757,19 +10757,19 @@
         <v>1.75</v>
       </c>
       <c r="S65" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="T65" t="n">
         <v>2.16</v>
       </c>
       <c r="U65" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="V65" t="n">
         <v>1.23</v>
       </c>
       <c r="W65" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X65" t="n">
         <v>1.06</v>
@@ -10790,32 +10790,32 @@
         <v>5.2</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
       </c>
       <c r="AF65" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AG65" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK65" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>1.7</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="O66" t="n">
-        <v>3.72</v>
+        <v>5</v>
       </c>
       <c r="P66" t="n">
-        <v>4.53</v>
+        <v>6</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK66" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>
@@ -11078,19 +11078,19 @@
         <v>1.59</v>
       </c>
       <c r="T67" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U67" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="V67" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W67" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X67" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y67" t="n">
         <v>1.55</v>
@@ -11105,16 +11105,16 @@
         <v>1.38</v>
       </c>
       <c r="AC67" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AD67" t="n">
         <v>1.09</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AG67" t="n">
         <v>1.58</v>
@@ -11234,22 +11234,22 @@
         <v>1.87</v>
       </c>
       <c r="S68" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="T68" t="n">
         <v>2.28</v>
       </c>
       <c r="U68" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="V68" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W68" t="n">
         <v>1.02</v>
       </c>
       <c r="X68" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y68" t="n">
         <v>1.48</v>
@@ -11264,13 +11264,13 @@
         <v>1.46</v>
       </c>
       <c r="AC68" t="n">
-        <v>5.4</v>
+        <v>4.65</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF68" t="n">
         <v>2.11</v>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="AJ68" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK68" t="n">
         <v>1.65</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.93</v>
+        <v>3.41</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6</v>
+        <v>2.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.41</v>
+        <v>1.93</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>2.03</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="O15" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="U15" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.42</v>
+        <v>3.04</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.14</v>
+        <v>1.73</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.95</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.95</v>
+        <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="P17" t="n">
-        <v>3.35</v>
+        <v>2.11</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="O18" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P18" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="R18" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="S18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.22</v>
       </c>
-      <c r="T18" t="n">
-        <v>4</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.15</v>
-      </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.72</v>
+        <v>7.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF18" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AG18" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>4.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.87</v>
+        <v>5.58</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>2.01</v>
       </c>
       <c r="R19" t="n">
-        <v>2.08</v>
+        <v>2.29</v>
       </c>
       <c r="S19" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="U19" t="n">
-        <v>3.16</v>
+        <v>2.56</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.02</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Y19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.09</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.53</v>
+        <v>2.17</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>3.88</v>
+        <v>1.24</v>
       </c>
       <c r="O20" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>7.5</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK20" t="n">
         <v>4.2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.22</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>3.67</v>
+        <v>4.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.11</v>
+        <v>1.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="U21" t="n">
-        <v>2.59</v>
+        <v>2.12</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.58</v>
+        <v>5.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.88</v>
+        <v>2.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.59</v>
+        <v>2.23</v>
       </c>
       <c r="O22" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P22" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U22" t="n">
         <v>2.25</v>
       </c>
-      <c r="S22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.5</v>
-      </c>
       <c r="V22" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB22" t="n">
         <v>2.17</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.24</v>
+        <v>2.59</v>
       </c>
       <c r="O23" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>7.5</v>
+        <v>2.28</v>
       </c>
       <c r="Q23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="AA23" t="n">
         <v>1.6</v>
       </c>
-      <c r="R23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V23" t="n">
-        <v>2</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AB23" t="n">
-        <v>3.72</v>
+        <v>2.17</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.72</v>
+        <v>2.52</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.07</v>
+        <v>1.41</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="AK23" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.23</v>
+        <v>3.88</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.74</v>
+        <v>1.64</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.75</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U24" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="V24" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.43</v>
+        <v>2.14</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.21</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA25" t="n">
         <v>1.53</v>
       </c>
-      <c r="O25" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="P25" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.08</v>
+        <v>2.88</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.17</v>
+        <v>1.05</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.86</v>
+        <v>2.3</v>
       </c>
       <c r="O26" t="n">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="S26" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="T26" t="n">
-        <v>4.5</v>
+        <v>2.47</v>
       </c>
       <c r="U26" t="n">
-        <v>1.87</v>
+        <v>3.16</v>
       </c>
       <c r="V26" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="W26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.22</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AE26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.85</v>
       </c>
-      <c r="AE26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AG26" t="n">
-        <v>3.08</v>
+        <v>1.75</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>8.6</v>
+        <v>1.55</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>3.66</v>
       </c>
       <c r="P27" t="n">
-        <v>1.29</v>
+        <v>6.44</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.75</v>
+        <v>2.15</v>
       </c>
       <c r="R27" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="S27" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5</v>
+        <v>2.53</v>
       </c>
       <c r="U27" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.4</v>
+        <v>2.78</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.38</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.19</v>
+        <v>1.03</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>2.88</v>
+        <v>1.13</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.05</v>
+        <v>2.14</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="O28" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>3.87</v>
+        <v>3.35</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="O29" t="n">
-        <v>3.66</v>
+        <v>3.76</v>
       </c>
       <c r="P29" t="n">
-        <v>6.44</v>
+        <v>3.87</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="R29" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S29" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T29" t="n">
-        <v>2.53</v>
+        <v>3.36</v>
       </c>
       <c r="U29" t="n">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="V29" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="W29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.02</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.78</v>
+        <v>4.65</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.2</v>
+        <v>1.56</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>2.23</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.1</v>
+        <v>2.42</v>
       </c>
       <c r="AD29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.19</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.63</v>
+        <v>2.38</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>1.98</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>2.08</v>
+        <v>3.45</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="O33" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="P33" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.21</v>
+        <v>2.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3.6</v>
+        <v>2.98</v>
       </c>
       <c r="P34" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R34" t="n">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="S34" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="T34" t="n">
-        <v>3.22</v>
+        <v>2.38</v>
       </c>
       <c r="U34" t="n">
-        <v>2.4</v>
+        <v>3.18</v>
       </c>
       <c r="V34" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF34" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.98</v>
+        <v>3.4</v>
       </c>
       <c r="O36" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>3.45</v>
+        <v>2.08</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6248,22 +6248,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="O37" t="n">
-        <v>3.52</v>
+        <v>2.95</v>
       </c>
       <c r="P37" t="n">
-        <v>4.17</v>
+        <v>3.2</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.54</v>
+        <v>1.71</v>
       </c>
       <c r="O41" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="P41" t="n">
-        <v>2.11</v>
+        <v>3.72</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="R41" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="S41" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T41" t="n">
-        <v>3.78</v>
+        <v>4.25</v>
       </c>
       <c r="U41" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="V41" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="W41" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X41" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41" t="n">
         <v>1.1</v>
       </c>
       <c r="Z41" t="n">
-        <v>5.09</v>
+        <v>6.15</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.71</v>
+        <v>2.54</v>
       </c>
       <c r="O42" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="P42" t="n">
-        <v>3.72</v>
+        <v>2.11</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.1</v>
+        <v>3.04</v>
       </c>
       <c r="R42" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="S42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W42" t="n">
         <v>1.18</v>
       </c>
-      <c r="T42" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.21</v>
-      </c>
       <c r="X42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
         <v>1.1</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.15</v>
+        <v>5.09</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB42" t="n">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="AC42" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
         <v>1.95</v>
       </c>
       <c r="U43" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="V43" t="n">
         <v>1.15</v>
@@ -7286,7 +7286,7 @@
         <v>3.08</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC43" t="n">
         <v>6.3</v>
@@ -7562,16 +7562,16 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O45" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="P45" t="n">
-        <v>4.33</v>
+        <v>4.81</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="R45" t="n">
         <v>1.8</v>
@@ -7595,7 +7595,7 @@
         <v>1.13</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="Z45" t="n">
         <v>2.1</v>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.31</v>
+        <v>1.37</v>
       </c>
       <c r="O47" t="n">
-        <v>2.65</v>
+        <v>3.85</v>
       </c>
       <c r="P47" t="n">
-        <v>3.05</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="R47" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="S47" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="T47" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="U47" t="n">
-        <v>4.3</v>
+        <v>3.54</v>
       </c>
       <c r="V47" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="W47" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.09</v>
+        <v>2.63</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.04</v>
+        <v>2.32</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AC47" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AE47" t="n">
         <v>1.02</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.46</v>
+        <v>2.6</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7992,27 +7992,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,64 +8039,64 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="O48" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="P48" t="n">
-        <v>8.800000000000001</v>
+        <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="R48" t="n">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="S48" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="T48" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="U48" t="n">
-        <v>3.54</v>
+        <v>2.4</v>
       </c>
       <c r="V48" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="W48" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X48" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.32</v>
+        <v>1.67</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AC48" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.75</v>
+        <v>1.52</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.38</v>
+        <v>2.28</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8142,7 +8142,7 @@
         <v>0</v>
       </c>
       <c r="AU48" s="3" t="n">
-        <v>46187.64583333334</v>
+        <v>46187.66666666666</v>
       </c>
     </row>
     <row r="49">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8353,68 +8353,68 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,68 +8512,68 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,64 +8675,64 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="O52" t="n">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="P52" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AC52" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,64 +8834,64 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="O53" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="Z53" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AA53" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -8904,10 +8904,10 @@
         </is>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8993,64 +8993,64 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>1.81</v>
+        <v>1.33</v>
       </c>
       <c r="O54" t="n">
-        <v>3.05</v>
+        <v>5.58</v>
       </c>
       <c r="P54" t="n">
-        <v>3.9</v>
+        <v>7.22</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.56</v>
+        <v>1.67</v>
       </c>
       <c r="R54" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V54" t="n">
         <v>1.83</v>
       </c>
-      <c r="S54" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="U54" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.24</v>
-      </c>
       <c r="W54" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X54" t="n">
         <v>1.01</v>
       </c>
-      <c r="X54" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y54" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF54" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z54" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AG54" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="AJ54" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O55" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P55" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="R55" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="S55" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB55" t="n">
         <v>1.44</v>
       </c>
-      <c r="T55" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U55" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W55" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AC55" t="n">
-        <v>4</v>
+        <v>5.45</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>1.14</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,80 +9311,80 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="O56" t="n">
-        <v>5.58</v>
+        <v>3.2</v>
       </c>
       <c r="P56" t="n">
-        <v>7.22</v>
+        <v>4.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="R56" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="S56" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56" t="n">
         <v>1.14</v>
       </c>
-      <c r="T56" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK56" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -9587,7 +9587,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -9629,64 +9629,64 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O58" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="P58" t="n">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R58" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S58" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="T58" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="U58" t="n">
         <v>3.75</v>
       </c>
       <c r="V58" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W58" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X58" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AC58" t="n">
-        <v>4.35</v>
+        <v>5.1</v>
       </c>
       <c r="AD58" t="n">
         <v>1.13</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
         </is>
       </c>
       <c r="AJ58" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK58" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -9746,7 +9746,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -9788,64 +9788,64 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O59" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="P59" t="n">
-        <v>3.55</v>
+        <v>2.55</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R59" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="S59" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="T59" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="U59" t="n">
         <v>3.75</v>
       </c>
       <c r="V59" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X59" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AC59" t="n">
-        <v>5.1</v>
+        <v>4.35</v>
       </c>
       <c r="AD59" t="n">
         <v>1.13</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF59" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="AJ59" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,64 +10583,64 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="O64" t="n">
-        <v>3.72</v>
+        <v>2.87</v>
       </c>
       <c r="P64" t="n">
-        <v>4.53</v>
+        <v>3.6</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.7</v>
+        <v>2.72</v>
       </c>
       <c r="AB64" t="n">
-        <v>2.1</v>
+        <v>1.46</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10653,10 +10653,10 @@
         </is>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,80 +10742,80 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>2.14</v>
+        <v>1.33</v>
       </c>
       <c r="O65" t="n">
-        <v>2.87</v>
+        <v>5</v>
       </c>
       <c r="P65" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.92</v>
+        <v>1.75</v>
       </c>
       <c r="R65" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="S65" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="T65" t="n">
-        <v>2.16</v>
+        <v>4.5</v>
       </c>
       <c r="U65" t="n">
-        <v>3.4</v>
+        <v>1.99</v>
       </c>
       <c r="V65" t="n">
-        <v>1.23</v>
+        <v>1.72</v>
       </c>
       <c r="W65" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X65" t="n">
         <v>1.01</v>
       </c>
-      <c r="X65" t="n">
+      <c r="Y65" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y65" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK65" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10901,64 +10901,64 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="O66" t="n">
-        <v>5</v>
+        <v>3.72</v>
       </c>
       <c r="P66" t="n">
-        <v>6</v>
+        <v>4.53</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.78</v>
+        <v>2.1</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -10971,10 +10971,10 @@
         </is>
       </c>
       <c r="AJ66" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK66" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.93</v>
+        <v>3.41</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>2.03</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>3.52</v>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>3.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.28</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="P13" t="n">
-        <v>3.47</v>
+        <v>2.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="P14" t="n">
-        <v>2.78</v>
+        <v>3.47</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.95</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
-        <v>3.95</v>
+        <v>3.67</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>2.59</v>
       </c>
       <c r="V15" t="n">
-        <v>1.79</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.36</v>
+        <v>1.77</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.86</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.88</v>
+        <v>1.32</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.31</v>
+        <v>1.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="O16" t="n">
-        <v>4.05</v>
+        <v>3.76</v>
       </c>
       <c r="P16" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="R16" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="U16" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="V16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.72</v>
+        <v>4.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.72</v>
+        <v>2.23</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.96</v>
+        <v>2.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>1.95</v>
       </c>
       <c r="O17" t="n">
-        <v>3.67</v>
+        <v>3.95</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>3.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="U17" t="n">
-        <v>2.59</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.58</v>
+        <v>6.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.77</v>
+        <v>1.36</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.88</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.32</v>
+        <v>1.88</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>3.04</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="O18" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,80 +3428,80 @@
         </is>
       </c>
       <c r="N19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK19" t="n">
         <v>1.53</v>
-      </c>
-      <c r="O19" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="P19" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.17</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>3.66</v>
       </c>
       <c r="P20" t="n">
-        <v>7.5</v>
+        <v>6.44</v>
       </c>
       <c r="Q20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.6</v>
       </c>
-      <c r="R20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V20" t="n">
-        <v>2</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>3.72</v>
-      </c>
       <c r="AC20" t="n">
-        <v>1.72</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.07</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.45</v>
+        <v>1.03</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.61</v>
+        <v>2.15</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK20" t="n">
-        <v>4.2</v>
+        <v>2.14</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T21" t="n">
         <v>4.5</v>
       </c>
-      <c r="O21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.22</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.14</v>
-      </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.35</v>
+        <v>3.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.42</v>
+        <v>3.08</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.23</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.74</v>
+        <v>1.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.75</v>
+        <v>4.4</v>
       </c>
       <c r="R22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB22" t="n">
         <v>2.35</v>
       </c>
-      <c r="S22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="AC22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>2.25</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK22" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.59</v>
+        <v>3.88</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.28</v>
+        <v>1.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>2.25</v>
+        <v>2.61</v>
       </c>
       <c r="S23" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="T23" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="U23" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="W23" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.27</v>
+        <v>5.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.52</v>
+        <v>2.14</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>3.88</v>
+        <v>8.6</v>
       </c>
       <c r="O24" t="n">
+        <v>5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z24" t="n">
         <v>4.4</v>
       </c>
-      <c r="P24" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="T24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AA24" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.53</v>
+        <v>1.83</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,80 +4382,80 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>8.6</v>
+        <v>1.71</v>
       </c>
       <c r="O25" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="P25" t="n">
-        <v>1.29</v>
+        <v>3.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.75</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="S25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.25</v>
       </c>
-      <c r="T25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AK25" t="n">
-        <v>1.05</v>
+        <v>1.95</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="P26" t="n">
-        <v>2.87</v>
+        <v>7.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="R26" t="n">
-        <v>2.08</v>
+        <v>3.15</v>
       </c>
       <c r="S26" t="n">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="T26" t="n">
-        <v>2.47</v>
+        <v>4.6</v>
       </c>
       <c r="U26" t="n">
-        <v>3.16</v>
+        <v>1.83</v>
       </c>
       <c r="V26" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.62</v>
+        <v>3.72</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.9</v>
+        <v>1.72</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>2.07</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.04</v>
+        <v>1.45</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.53</v>
+        <v>4.2</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.55</v>
+        <v>2.23</v>
       </c>
       <c r="O27" t="n">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="P27" t="n">
-        <v>6.44</v>
+        <v>2.74</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="S27" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T27" t="n">
-        <v>2.53</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="V27" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.1</v>
+        <v>2.43</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.95</v>
+        <v>2.59</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>3.35</v>
+        <v>2.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="O29" t="n">
-        <v>3.76</v>
+        <v>4.28</v>
       </c>
       <c r="P29" t="n">
-        <v>3.87</v>
+        <v>5.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.31</v>
+        <v>2.01</v>
       </c>
       <c r="R29" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S29" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T29" t="n">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="U29" t="n">
-        <v>2.23</v>
+        <v>2.56</v>
       </c>
       <c r="V29" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W29" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
         <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.65</v>
+        <v>3.65</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.42</v>
+        <v>2.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,22 +5453,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="P32" t="n">
-        <v>3.45</v>
+        <v>4.17</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="O33" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="P33" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.73</v>
+        <v>1.98</v>
       </c>
       <c r="O34" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Keflavík</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.71</v>
+        <v>2.54</v>
       </c>
       <c r="O41" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="P41" t="n">
-        <v>3.72</v>
+        <v>2.11</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.1</v>
+        <v>3.04</v>
       </c>
       <c r="R41" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="S41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.18</v>
       </c>
-      <c r="T41" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.21</v>
-      </c>
       <c r="X41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41" t="n">
         <v>1.1</v>
       </c>
       <c r="Z41" t="n">
-        <v>6.15</v>
+        <v>5.09</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AB41" t="n">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="AC41" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.89</v>
+        <v>2.72</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.03</v>
+        <v>1.4</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Keflavík</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.54</v>
+        <v>1.71</v>
       </c>
       <c r="O42" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="P42" t="n">
-        <v>2.11</v>
+        <v>3.72</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="R42" t="n">
-        <v>2.33</v>
+        <v>2.62</v>
       </c>
       <c r="S42" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T42" t="n">
-        <v>3.78</v>
+        <v>4.25</v>
       </c>
       <c r="U42" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="V42" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="W42" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
         <v>1.1</v>
       </c>
       <c r="Z42" t="n">
-        <v>5.09</v>
+        <v>6.15</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.49</v>
+        <v>3</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P44" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R44" t="n">
         <v>1.8</v>
       </c>
-      <c r="O44" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P44" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O45" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="P45" t="n">
-        <v>4.81</v>
+        <v>4.65</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AC45" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7997,22 +7997,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8166,12 +8166,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>3.13</v>
+        <v>1.81</v>
       </c>
       <c r="O49" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.68</v>
+        <v>2.56</v>
       </c>
       <c r="R49" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="S49" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="T49" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="U49" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="V49" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="W49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE49" t="n">
         <v>1.03</v>
       </c>
-      <c r="X49" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AF49" t="n">
-        <v>1.88</v>
+        <v>2.32</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,64 +8357,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="O50" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="P50" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="R50" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="S50" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V50" t="n">
         <v>1.53</v>
       </c>
-      <c r="T50" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.25</v>
-      </c>
       <c r="W50" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X50" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.87</v>
+        <v>1.67</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.39</v>
+        <v>2.15</v>
       </c>
       <c r="AC50" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.51</v>
+        <v>2.28</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8427,10 +8427,10 @@
         </is>
       </c>
       <c r="AJ50" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8512,68 +8512,68 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8675,64 +8675,64 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="O52" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="Z52" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -8792,7 +8792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -8834,80 +8834,80 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2.41</v>
+        <v>3.13</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="P53" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.25</v>
+        <v>4.68</v>
       </c>
       <c r="R53" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S53" t="n">
         <v>1.5</v>
       </c>
       <c r="T53" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="U53" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="V53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AK53" t="n">
         <v>1.25</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X53" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1.54</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -9120,12 +9120,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -9152,64 +9152,64 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="O55" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="P55" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R55" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="S55" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T55" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="U55" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="V55" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W55" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X55" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AC55" t="n">
-        <v>5.45</v>
+        <v>5.4</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE55" t="n">
         <v>1.03</v>
       </c>
       <c r="AF55" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         </is>
       </c>
       <c r="AJ55" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -9311,64 +9311,64 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="O56" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="P56" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z56" t="n">
         <v>2</v>
       </c>
-      <c r="S56" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T56" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U56" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X56" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AA56" t="n">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="AC56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9381,10 +9381,10 @@
         </is>
       </c>
       <c r="AJ56" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -10382,7 +10382,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -10420,17 +10420,17 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -10583,80 +10583,80 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>2.14</v>
+        <v>1.33</v>
       </c>
       <c r="O64" t="n">
-        <v>2.87</v>
+        <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.92</v>
+        <v>1.75</v>
       </c>
       <c r="R64" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="S64" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="T64" t="n">
-        <v>2.16</v>
+        <v>4.5</v>
       </c>
       <c r="U64" t="n">
-        <v>3.4</v>
+        <v>1.99</v>
       </c>
       <c r="V64" t="n">
-        <v>1.23</v>
+        <v>1.72</v>
       </c>
       <c r="W64" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X64" t="n">
         <v>1.01</v>
       </c>
-      <c r="X64" t="n">
+      <c r="Y64" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64" t="n">
         <v>1.06</v>
       </c>
-      <c r="Y64" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z64" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA64" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD64" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF64" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG64" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AK64" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -10742,80 +10742,80 @@
         </is>
       </c>
       <c r="N65" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P65" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65" t="n">
         <v>1.33</v>
       </c>
-      <c r="O65" t="n">
-        <v>5</v>
-      </c>
-      <c r="P65" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R65" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S65" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T65" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U65" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V65" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W65" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X65" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y65" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z65" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA65" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK65" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -10897,17 +10897,17 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -11028,12 +11028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -11060,64 +11060,64 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O67" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P67" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="R67" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="S67" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T67" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="U67" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="V67" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="W67" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X67" t="n">
         <v>1.07</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AC67" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11130,10 +11130,10 @@
         </is>
       </c>
       <c r="AJ67" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AK67" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -11187,12 +11187,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -11219,64 +11219,64 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O68" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P68" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R68" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="S68" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T68" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="U68" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="V68" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="W68" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X68" t="n">
         <v>1.07</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.44</v>
+        <v>2.19</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AC68" t="n">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE68" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11289,10 +11289,10 @@
         </is>
       </c>
       <c r="AJ68" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AK68" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AL68" t="n">
         <v>0</v>

--- a/jogos_2026-06-14.xlsx
+++ b/jogos_2026-06-14.xlsx
@@ -734,55 +734,55 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB2" t="n">
         <v>2.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="O3" t="n">
         <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>3.6</v>
+        <v>2.03</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>5.08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
         <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="AA6" t="n">
         <v>1.77</v>
@@ -1409,7 +1409,7 @@
         <v>2.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
         <v>1.09</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>3.52</v>
+        <v>3.05</v>
       </c>
       <c r="P9" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>3.62</v>
       </c>
       <c r="P13" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="Q13" t="n">
         <v>2.75</v>
@@ -2504,28 +2504,28 @@
         <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.05</v>
+        <v>4.27</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
         <v>1.57</v>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK13" t="n">
         <v>1.6</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="O14" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P14" t="n">
-        <v>3.47</v>
+        <v>3.89</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.11</v>
+        <v>3.1</v>
       </c>
       <c r="Q15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB15" t="n">
         <v>3.4</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>3.08</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,28 +2951,28 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.82</v>
+        <v>2.23</v>
       </c>
       <c r="O16" t="n">
-        <v>3.76</v>
+        <v>3.55</v>
       </c>
       <c r="P16" t="n">
-        <v>3.87</v>
+        <v>2.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="R16" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="S16" t="n">
         <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V16" t="n">
         <v>1.57</v>
@@ -2981,28 +2981,28 @@
         <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF16" t="n">
         <v>1.5</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
         <v>2.5</v>
       </c>
       <c r="S17" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T17" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="W17" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.6</v>
+        <v>5.72</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="P18" t="n">
-        <v>3.35</v>
+        <v>6.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="P19" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q19" t="n">
         <v>3.1</v>
@@ -3443,37 +3443,37 @@
         <v>2.08</v>
       </c>
       <c r="S19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W19" t="n">
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="AD19" t="n">
         <v>1.22</v>
@@ -3482,10 +3482,10 @@
         <v>1.04</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.75</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,65 +3587,65 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="O20" t="n">
-        <v>3.66</v>
+        <v>6.5</v>
       </c>
       <c r="P20" t="n">
-        <v>6.44</v>
+        <v>8.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.15</v>
+        <v>1.56</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1</v>
+        <v>3.08</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="T20" t="n">
-        <v>2.53</v>
+        <v>4.6</v>
       </c>
       <c r="U20" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.78</v>
+        <v>7</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG20" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.14</v>
+        <v>3.98</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="O21" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S21" t="n">
         <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AD21" t="n">
         <v>1.85</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.36</v>
       </c>
-      <c r="AF21" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AG21" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,80 +3905,80 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>1.47</v>
       </c>
       <c r="O22" t="n">
-        <v>4.1</v>
+        <v>4.28</v>
       </c>
       <c r="P22" t="n">
-        <v>1.6</v>
+        <v>5.58</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.4</v>
+        <v>2.01</v>
       </c>
       <c r="R22" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="S22" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T22" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="V22" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="W22" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
         <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AC22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK22" t="n">
         <v>2.17</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.14</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3.88</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q23" t="n">
         <v>4.4</v>
       </c>
-      <c r="P23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.2</v>
-      </c>
       <c r="R23" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="S23" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T23" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="U23" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V23" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X23" t="n">
         <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AD23" t="n">
         <v>1.67</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="P24" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="Q24" t="n">
-        <v>6.75</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="S24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.25</v>
       </c>
-      <c r="T24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="O25" t="n">
-        <v>4.05</v>
+        <v>3.55</v>
       </c>
       <c r="P25" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="R25" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="V25" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X25" t="n">
         <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.72</v>
+        <v>4.65</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.72</v>
+        <v>2.23</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.96</v>
+        <v>2.42</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>1.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>2.12</v>
       </c>
       <c r="O26" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>7.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="O27" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="P27" t="n">
-        <v>2.74</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.75</v>
+        <v>3.38</v>
       </c>
       <c r="R27" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="S27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.25</v>
       </c>
-      <c r="T27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AK27" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.59</v>
+        <v>8.6</v>
       </c>
       <c r="O28" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>7.42</v>
       </c>
       <c r="R28" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB28" t="n">
         <v>2.25</v>
       </c>
-      <c r="S28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AC28" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.52</v>
+        <v>2.94</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.53</v>
+        <v>2.65</v>
       </c>
       <c r="O29" t="n">
-        <v>4.28</v>
+        <v>3.08</v>
       </c>
       <c r="P29" t="n">
-        <v>5.58</v>
+        <v>2.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.01</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S29" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T29" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U29" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V29" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.65</v>
+        <v>4.27</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.86</v>
+        <v>2.32</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,22 +5294,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="O32" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="P32" t="n">
-        <v>4.17</v>
+        <v>2.92</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,22 +5612,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="O33" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="P33" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P34" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5930,22 +5930,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.21</v>
+        <v>3.4</v>
       </c>
       <c r="O35" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>3.4</v>
+        <v>1.98</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P36" t="n">
-        <v>2.08</v>
+        <v>3.45</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6617,16 +6617,16 @@
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R39" t="n">
         <v>2.4</v>
       </c>
       <c r="S39" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T39" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="U39" t="n">
         <v>2.5</v>
@@ -6635,19 +6635,19 @@
         <v>1.5</v>
       </c>
       <c r="W39" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X39" t="n">
         <v>1.02</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z39" t="n">
         <v>4.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB39" t="n">
         <v>2.12</v>
@@ -6659,7 +6659,7 @@
         <v>1.44</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF39" t="n">
         <v>1.62</v>
@@ -6681,7 +6681,7 @@
         <v>1.17</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6770,10 +6770,10 @@
         <v>2.8</v>
       </c>
       <c r="O40" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P40" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q40" t="n">
         <v>3.5</v>
@@ -6803,28 +6803,28 @@
         <v>1.23</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6926,19 +6926,19 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="P41" t="n">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="Q41" t="n">
         <v>3.04</v>
       </c>
       <c r="R41" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S41" t="n">
         <v>1.2</v>
@@ -6953,7 +6953,7 @@
         <v>1.66</v>
       </c>
       <c r="W41" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X41" t="n">
         <v>1.02</v>
@@ -6971,7 +6971,7 @@
         <v>2.49</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="AD41" t="n">
         <v>1.68</v>
@@ -7088,7 +7088,7 @@
         <v>1.71</v>
       </c>
       <c r="O42" t="n">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="P42" t="n">
         <v>3.72</v>
@@ -7097,7 +7097,7 @@
         <v>2.1</v>
       </c>
       <c r="R42" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S42" t="n">
         <v>1.18</v>
@@ -7121,7 +7121,7 @@
         <v>1.1</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.15</v>
+        <v>5.2</v>
       </c>
       <c r="AA42" t="n">
         <v>1.36</v>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7265,7 +7265,7 @@
         <v>1.95</v>
       </c>
       <c r="U43" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="V43" t="n">
         <v>1.15</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="P44" t="n">
-        <v>4.81</v>
+        <v>4.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AC44" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="P45" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R45" t="n">
         <v>1.8</v>
       </c>
-      <c r="O45" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P45" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>1.12</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="Z46" t="n">
         <v>2.07</v>
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="O47" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P47" t="n">
-        <v>8.800000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="Q47" t="n">
         <v>1.95</v>
@@ -7910,7 +7910,7 @@
         <v>1.04</v>
       </c>
       <c r="X47" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y47" t="n">
         <v>1.43</v>
@@ -7928,10 +7928,10 @@
         <v>4.75</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF47" t="n">
         <v>2.75</v>
@@ -7997,7 +7997,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8035,68 +8035,68 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8156,22 +8156,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>1.81</v>
+        <v>2.15</v>
       </c>
       <c r="O49" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P49" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="R49" t="n">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="S49" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="T49" t="n">
-        <v>2.31</v>
+        <v>3.3</v>
       </c>
       <c r="U49" t="n">
-        <v>3.82</v>
+        <v>2.4</v>
       </c>
       <c r="V49" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="W49" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X49" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AC49" t="n">
-        <v>5.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.32</v>
+        <v>1.52</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8315,22 +8315,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8357,80 +8357,80 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="O50" t="n">
-        <v>3.25</v>
+        <v>5.58</v>
       </c>
       <c r="P50" t="n">
-        <v>3</v>
+        <v>7.22</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="R50" t="n">
-        <v>2.32</v>
+        <v>2.85</v>
       </c>
       <c r="S50" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="T50" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X50" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB50" t="n">
         <v>3.3</v>
       </c>
-      <c r="U50" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V50" t="n">
+      <c r="AC50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF50" t="n">
         <v>1.53</v>
       </c>
-      <c r="W50" t="n">
+      <c r="AG50" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50" t="n">
         <v>1.1</v>
       </c>
-      <c r="X50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK50" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -8516,16 +8516,16 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O51" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P51" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R51" t="n">
         <v>2</v>
@@ -8534,46 +8534,46 @@
         <v>1.44</v>
       </c>
       <c r="T51" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="U51" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="V51" t="n">
         <v>1.3</v>
       </c>
       <c r="W51" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X51" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AC51" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF51" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8586,10 +8586,10 @@
         </is>
       </c>
       <c r="AJ51" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK51" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -8671,68 +8671,68 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.69</v>
+        <v>0</v>
